--- a/testdata/configurationUAT/execute.xlsx
+++ b/testdata/configurationUAT/execute.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -12,7 +12,8 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="358">
   <si>
     <t>App</t>
   </si>
@@ -73,889 +74,964 @@
     <t>data</t>
   </si>
   <si>
+    <t>Product_Summary-Loan_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70780</t>
+  </si>
+  <si>
+    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70781</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70782</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_6</t>
+  </si>
+  <si>
+    <t>C70783</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_2</t>
+  </si>
+  <si>
+    <t>C70784</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_3</t>
+  </si>
+  <si>
+    <t>C70785</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_4</t>
+  </si>
+  <si>
+    <t>C70786</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_5</t>
+  </si>
+  <si>
+    <t>C70787</t>
+  </si>
+  <si>
+    <t>Current_Accounts-Transactions_Details-Create_Confirmation_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70788</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Search_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70789</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70790</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70791</t>
+  </si>
+  <si>
+    <t>Product_Summary_Edit_Product_View_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70792</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70793</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70794</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70795</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70797</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Foreign_Account</t>
+  </si>
+  <si>
+    <t>C70798</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Credit_Card</t>
+  </si>
+  <si>
+    <t>C70799</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Savings_Account</t>
+  </si>
+  <si>
+    <t>C70800</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Term_Deposit_Accounts</t>
+  </si>
+  <si>
+    <t>C70801</t>
+  </si>
+  <si>
+    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Loan_Accounts</t>
+  </si>
+  <si>
+    <t>C70802</t>
+  </si>
+  <si>
+    <t>Product_Summary-Term_Deposits_Lists_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70803</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts_Transactions_Filter_By_Date_CustomDateRange_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70804</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70805</t>
+  </si>
+  <si>
+    <t>Current_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70806</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Domestic_Accounts-List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70807</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70808</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70809</t>
+  </si>
+  <si>
+    <t>Product_Summary-Savings_Accounts_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70810</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_Card_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70811</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70812</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70813</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Product_Details-Financial-Details_Is_Not_Visible_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70814</t>
+  </si>
+  <si>
+    <t>Product_Summary-Credit_Card_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70815</t>
+  </si>
+  <si>
+    <t>Term_Deposit_Accounts_Details_Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70816</t>
+  </si>
+  <si>
+    <t>Term_Deposits_Accounts-Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70817</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70818</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Foreign_Accounts_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70819</t>
+  </si>
+  <si>
+    <t>Manage_Products-Hide/Show_account_on_Product_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70820</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70821</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Cancel_Button_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70822</t>
+  </si>
+  <si>
+    <t>Credit_cards_transactions_filter_by_date-Date_Picker_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70823</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter_Date_Picker_invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70824</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter-Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70825</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70826</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70827</t>
+  </si>
+  <si>
+    <t>Product_Summary-Term_Deposit_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70828</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Product_Details_Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70829</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer-Flow_Disruption_Cancel/Back_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70830</t>
+  </si>
+  <si>
+    <t>Credit_cards-Transactions-Filter_Multiple_Filter_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70831</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Camera_Permission_Reject_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70832</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70833</t>
+  </si>
+  <si>
+    <t>Products-Current_Account-Cheques_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70834</t>
+  </si>
+  <si>
+    <t>Products-Current_Account-Cheques-Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70835</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Back_Button_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70836</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70837</t>
+  </si>
+  <si>
+    <t>Products-Current_Account-Cheques-Input_Fields-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70838</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Create_New_Recipient_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70839</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Modify_Data_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70840</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-In_Future_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70841</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70842</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE-invalid_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70843</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70844</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT-invalid_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70845</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_STATUS_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70846</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Product_On_The_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70847</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70848</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Details-Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70849</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70850</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70851</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70852</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70853</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70854</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70855</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-CREATE_CONFIRMATION_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70856</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Payments_Transaction_List_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70857</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70858</t>
+  </si>
+  <si>
+    <t>Authentication-Mobile_Login-Logout_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70859</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Successful_Payment_Via_The_Scan_And_Pay_Option_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70860</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-QR_Code_Not_Recognized_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70861</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Payment_Via_The_Scan_And_Pay_Option-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70862</t>
+  </si>
+  <si>
+    <t>Mobile_Login-Generate_OTP-mToken_From_Login_Screen_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70863</t>
+  </si>
+  <si>
+    <t>Term_Deposit_Accounts_Details_Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70864</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]-Internal_Urgent_Payment</t>
+  </si>
+  <si>
+    <t>C70865</t>
+  </si>
+  <si>
+    <t>CURRENT_FOREIGN_ACCOUNTS-TRANSACTIONS-OVERVIEW_BY_DIFFERENT_CURRENCIES_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70866</t>
+  </si>
+  <si>
+    <t>General-Login_Page_Elements-Buttons-Activated_Users_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70867</t>
+  </si>
+  <si>
+    <t>Authentication-Login_In_MOB-Login_Page_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70868</t>
+  </si>
+  <si>
+    <t>Authentication-Login_With_PIN_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70869</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70870</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70871</t>
+  </si>
+  <si>
+    <t>Current_Foreign-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70872</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70873</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70874</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70875</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Internal_Non_Urgent_Payment</t>
+  </si>
+  <si>
+    <t>C70876</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Input-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70877</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70878</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter-invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70879</t>
+  </si>
+  <si>
+    <t>CURRENT_ACCOUNTS_RSD-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70880</t>
+  </si>
+  <si>
+    <t>CURRENT_FOREIGN_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70881</t>
+  </si>
+  <si>
+    <t>SAVINGS_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70882</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70883</t>
+  </si>
+  <si>
+    <t>Payments-Scan_And_Pay-Domestic_Payment_Page_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70884</t>
+  </si>
+  <si>
+    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Debit_Cards</t>
+  </si>
+  <si>
+    <t>C70885</t>
+  </si>
+  <si>
+    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70886</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70887</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Transactions_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70888</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_No_Model</t>
+  </si>
+  <si>
+    <t>C70889</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_No_Model</t>
+  </si>
+  <si>
+    <t>C70890</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_11</t>
+  </si>
+  <si>
+    <t>C70891</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_97</t>
+  </si>
+  <si>
+    <t>C70892</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_11-invalid</t>
+  </si>
+  <si>
+    <t>C70893</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_97-invalid</t>
+  </si>
+  <si>
+    <t>C70894</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_Model_11</t>
+  </si>
+  <si>
+    <t>C70895</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_Model_97</t>
+  </si>
+  <si>
+    <t>C70896</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Model_97</t>
+  </si>
+  <si>
+    <t>C70897</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[MOB_ANDROID]-Debit_Cards</t>
+  </si>
+  <si>
+    <t>C70898</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[MOB_ANDROID]-Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70899</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-PAYMENTS_LIST_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70900</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70901</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70902</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_List_Of_Transactions_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70903</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_Cancel_Payment_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70904</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70905</t>
+  </si>
+  <si>
+    <t>Current_Domestic_Accounts-Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70906</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70907</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70908</t>
+  </si>
+  <si>
+    <t>Mobile_Login-Generate_OTP-Inside_30_Seconds_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70909</t>
+  </si>
+  <si>
+    <t>Mobile_Authorizations-Successful_Authorization_Of_Payment_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70910</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_Pricelist_[MOB_ANDROID]-Overview</t>
+  </si>
+  <si>
+    <t>C70911</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[MOB_ANDROID]-Buy_From_Payment</t>
+  </si>
+  <si>
+    <t>C70912</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[MOB_ANDROID]-Sell_From_Payment</t>
+  </si>
+  <si>
+    <t>C70913</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Purpose_Code_289_invalid</t>
+  </si>
+  <si>
+    <t>C70914</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Without_Reference_Number_invalid</t>
+  </si>
+  <si>
+    <t>C70915</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Predefined_Date_Range_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70916</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_PRENESI_Confirm_Successful_Payments_Archive_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70917</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Overview_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70918</t>
+  </si>
+  <si>
+    <t>PAYMENTS-PAYMENTS_ARCHIVE-PAYMENTS_DETAILS_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70919</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Edit_Recipient_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70920</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Template_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70921</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70922</t>
+  </si>
+  <si>
+    <t>Manage_Products_Hide/Show_account_on_Product_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70923</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70924</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70925</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Statemants_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70926</t>
+  </si>
+  <si>
+    <t>C70927</t>
+  </si>
+  <si>
+    <t>C70928</t>
+  </si>
+  <si>
+    <t>C70929</t>
+  </si>
+  <si>
+    <t>C70930</t>
+  </si>
+  <si>
+    <t>C70931</t>
+  </si>
+  <si>
+    <t>C70932</t>
+  </si>
+  <si>
+    <t>C70933</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[ANDROID]</t>
+  </si>
+  <si>
+    <t>C70934</t>
+  </si>
+  <si>
     <t>on</t>
   </si>
   <si>
-    <t>Product_Summary-Loan_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70780</t>
-  </si>
-  <si>
-    <t>Product_Summary_Sorting_on_the_Product_Summary_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70781</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70782</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_6</t>
-  </si>
-  <si>
-    <t>C70783</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_2</t>
-  </si>
-  <si>
-    <t>C70784</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_3</t>
-  </si>
-  <si>
-    <t>C70785</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_4</t>
-  </si>
-  <si>
-    <t>C70786</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_5</t>
-  </si>
-  <si>
-    <t>C70787</t>
-  </si>
-  <si>
-    <t>Current_Accounts-Transactions_Details-Create_Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70788</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Search_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70789</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70790</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70791</t>
-  </si>
-  <si>
-    <t>Product_Summary_Edit_Product_View_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70792</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70793</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70794</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70795</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Domestic_Account</t>
-  </si>
-  <si>
-    <t>C70797</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Current_Foreign_Account</t>
-  </si>
-  <si>
-    <t>C70798</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Credit_Card</t>
-  </si>
-  <si>
-    <t>C70799</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Savings_Account</t>
-  </si>
-  <si>
-    <t>C70800</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Term_Deposit_Accounts</t>
-  </si>
-  <si>
-    <t>C70801</t>
-  </si>
-  <si>
-    <t>Product_Summary-Edit_Product_View-Edit_Name_Of_Account_[MOB_ANDROID]-Loan_Accounts</t>
-  </si>
-  <si>
-    <t>C70802</t>
-  </si>
-  <si>
-    <t>Product_Summary-Term_Deposits_Lists_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70803</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts_Transactions_Filter_By_Date_CustomDateRange_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70804</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70805</t>
-  </si>
-  <si>
-    <t>Current_Accounts_Transactions_Details_Transaction_Confirmation_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70806</t>
-  </si>
-  <si>
-    <t>Product_Summary-Current_Domestic_Accounts-List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70807</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70808</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70809</t>
-  </si>
-  <si>
-    <t>Product_Summary-Savings_Accounts_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70810</t>
-  </si>
-  <si>
-    <t>Credit_Cards_Details_Card_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70811</t>
-  </si>
-  <si>
-    <t>Credit_Cards_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70812</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70813</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Product_Details-Financial-Details_Is_Not_Visible_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70814</t>
-  </si>
-  <si>
-    <t>Product_Summary-Credit_Card_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70815</t>
-  </si>
-  <si>
-    <t>Term_Deposit_Accounts_Details_Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70816</t>
-  </si>
-  <si>
-    <t>Term_Deposits_Accounts-Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70817</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70818</t>
-  </si>
-  <si>
-    <t>Product_Summary-Current_Foreign_Accounts_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70819</t>
-  </si>
-  <si>
-    <t>Manage_Products-Hide/Show_account_on_Product_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70820</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70821</t>
-  </si>
-  <si>
-    <t>Payments_Domestic_Payments_Cancel_Button_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70822</t>
-  </si>
-  <si>
-    <t>Credit_cards_transactions_filter_by_date-Date_Picker_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70823</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions-Filter_Date_Picker_invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70824</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter-Filter_By_Type_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70825</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70826</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter-Filter_By_Amount_invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70827</t>
-  </si>
-  <si>
-    <t>Product_Summary-Term_Deposit_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70828</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Product_Details_Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70829</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer-Flow_Disruption_Cancel/Back_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70830</t>
-  </si>
-  <si>
-    <t>Credit_cards-Transactions-Filter_Multiple_Filter_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70831</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Camera_Permission_Reject_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70832</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70833</t>
-  </si>
-  <si>
-    <t>Products-Current_Account-Cheques_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70834</t>
-  </si>
-  <si>
-    <t>Products-Current_Account-Cheques-Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70835</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Back_Button_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70836</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Transactions-Filter-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70837</t>
-  </si>
-  <si>
-    <t>Products-Current_Account-Cheques-Input_Fields-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70838</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Create_New_Recipient_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70839</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Modify_Data_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70840</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-In_Future_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70841</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70842</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_DATE-invalid_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70843</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70844</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_AMOUNT-invalid_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70845</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-FILTER_PAYMENTS_BY_STATUS_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70846</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Product_On_The_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70847</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70848</t>
-  </si>
-  <si>
-    <t>Credit_Cards-Details-Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70849</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70850</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70851</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan-Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70852</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70853</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70854</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments-Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70855</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-CREATE_CONFIRMATION_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70856</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Archive_Payments_Transaction_List_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70857</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70858</t>
-  </si>
-  <si>
-    <t>Authentication-Mobile_Login-Logout_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70859</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Successful_Payment_Via_The_Scan_And_Pay_Option_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70860</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-QR_Code_Not_Recognized_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70861</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Payment_Via_The_Scan_And_Pay_Option-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70862</t>
-  </si>
-  <si>
-    <t>Mobile_Login-Generate_OTP-mToken_From_Login_Screen_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70863</t>
-  </si>
-  <si>
-    <t>Term_Deposit_Accounts_Details_Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70864</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]-Internal_Urgent_Payment</t>
-  </si>
-  <si>
-    <t>C70865</t>
-  </si>
-  <si>
-    <t>CURRENT_FOREIGN_ACCOUNTS-TRANSACTIONS-OVERVIEW_BY_DIFFERENT_CURRENCIES_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70866</t>
-  </si>
-  <si>
-    <t>General-Login_Page_Elements-Buttons-Activated_Users_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70867</t>
-  </si>
-  <si>
-    <t>Authentication-Login_In_MOB-Login_Page_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70868</t>
-  </si>
-  <si>
-    <t>Authentication-Login_With_PIN_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70869</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Account-Transactions-Filter_By_Type_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70870</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70871</t>
-  </si>
-  <si>
-    <t>Current_Foreign-Transactions-Filter-Multiple_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70872</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter-Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70873</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Filter-Clear_Filter_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70874</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions-Search_Invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70875</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Internal_Non_Urgent_Payment</t>
-  </si>
-  <si>
-    <t>C70876</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments-Input-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70877</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70878</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Payments-Filter-invalid_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70879</t>
-  </si>
-  <si>
-    <t>CURRENT_ACCOUNTS_RSD-STATEMANTS-FILTER_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70880</t>
-  </si>
-  <si>
-    <t>CURRENT_FOREIGN_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70881</t>
-  </si>
-  <si>
-    <t>SAVINGS_ACCOUNTS-STATEMANTS-FILTER_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70882</t>
-  </si>
-  <si>
-    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70883</t>
-  </si>
-  <si>
-    <t>Payments-Scan_And_Pay-Domestic_Payment_Page_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70884</t>
-  </si>
-  <si>
-    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Debit_Cards</t>
-  </si>
-  <si>
-    <t>C70885</t>
-  </si>
-  <si>
-    <t>Cards_Transactions_List-Filter_invalid_[MOB_ANDROID]-Credit_Cards</t>
-  </si>
-  <si>
-    <t>C70886</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Transactions_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70887</t>
-  </si>
-  <si>
-    <t>Savings_Accounts-Transactions_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70888</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_No_Model</t>
-  </si>
-  <si>
-    <t>C70889</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_No_Model</t>
-  </si>
-  <si>
-    <t>C70890</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_11</t>
-  </si>
-  <si>
-    <t>C70891</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_97</t>
-  </si>
-  <si>
-    <t>C70892</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_11-invalid</t>
-  </si>
-  <si>
-    <t>C70893</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Urgent_Payment_Model_97-invalid</t>
-  </si>
-  <si>
-    <t>C70894</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_Model_11</t>
-  </si>
-  <si>
-    <t>C70895</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-External_Non_Urgent_Payment_Model_97</t>
-  </si>
-  <si>
-    <t>C70896</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Model_97</t>
-  </si>
-  <si>
-    <t>C70897</t>
-  </si>
-  <si>
-    <t>Cards-Transactions_Details_[MOB_ANDROID]-Debit_Cards</t>
-  </si>
-  <si>
-    <t>C70898</t>
-  </si>
-  <si>
-    <t>Cards-Transactions_Details_[MOB_ANDROID]-Credit_Cards</t>
-  </si>
-  <si>
-    <t>C70899</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-PAYMENTS_LIST_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70900</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts-Transactions_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70901</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Transactions_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70902</t>
-  </si>
-  <si>
-    <t>Payments_Upcoming_Payments_List_Of_Transactions_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70903</t>
-  </si>
-  <si>
-    <t>Payments_Upcoming_Payments_Cancel_Payment_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70904</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70905</t>
-  </si>
-  <si>
-    <t>Current_Domestic_Accounts-Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70906</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Details-Financial_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70907</t>
-  </si>
-  <si>
-    <t>Loan_Accounts-Details-Account_Details_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70908</t>
-  </si>
-  <si>
-    <t>Mobile_Login-Generate_OTP-Inside_30_Seconds_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70909</t>
-  </si>
-  <si>
-    <t>Mobile_Authorizations-Successful_Authorization_Of_Payment_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70910</t>
-  </si>
-  <si>
-    <t>Payments_Currency_Exchange_Pricelist_[MOB_ANDROID]-Overview</t>
-  </si>
-  <si>
-    <t>C70911</t>
-  </si>
-  <si>
-    <t>Payments_Currency_Exchange_[MOB_ANDROID]-Buy_From_Payment</t>
-  </si>
-  <si>
-    <t>C70912</t>
-  </si>
-  <si>
-    <t>Payments_Currency_Exchange_[MOB_ANDROID]-Sell_From_Payment</t>
-  </si>
-  <si>
-    <t>C70913</t>
-  </si>
-  <si>
-    <t>5,</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Purpose_Code_289_invalid</t>
-  </si>
-  <si>
-    <t>C70914</t>
-  </si>
-  <si>
-    <t>Payments-Domestic_Payments_[MOB_ANDROID]-Budget_Urgent_Payment_Without_Reference_Number_invalid</t>
-  </si>
-  <si>
-    <t>C70915</t>
-  </si>
-  <si>
-    <t>Savings_Accounts_Transactions_Filter_By_Date_Predefined_Date_Range_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70916</t>
-  </si>
-  <si>
-    <t>Payments_Specific_Payment_PRENESI_Confirm_Successful_Payments_Archive_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70917</t>
-  </si>
-  <si>
-    <t>Payments_Payments_Overview_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70918</t>
-  </si>
-  <si>
-    <t>PAYMENTS-PAYMENTS_ARCHIVE-PAYMENTS_DETAILS_[ANDROID]</t>
-  </si>
-  <si>
-    <t>C70919</t>
-  </si>
-  <si>
-    <t>Payments_Recipient_Edit_Recipient_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70920</t>
-  </si>
-  <si>
-    <t>Payments_Recipient_Template_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70921</t>
-  </si>
-  <si>
-    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70922</t>
-  </si>
-  <si>
-    <t>Manage_Products_Hide/Show_account_on_Product_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70923</t>
-  </si>
-  <si>
-    <t>Current_Accounts_RSD_Statemants_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70924</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Statemants_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70925</t>
-  </si>
-  <si>
-    <t>Savings_Accounts_Statemants_List_[MOB_ANDROID]</t>
-  </si>
-  <si>
-    <t>C70926</t>
+    <t>Payments_Own_Account_Transfer_To_Card_[ANDROID]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70935</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Card_[ANDROID]-From_Saving_Account</t>
+  </si>
+  <si>
+    <t>C70936</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[ANDROID]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70937</t>
+  </si>
+  <si>
+    <t>Payments_Specific_Payment_Credit_Card_Repayment_[ANDROID]-From_Saving_Account</t>
+  </si>
+  <si>
+    <t>C70938</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[ANDROID]-Internal_Transfer</t>
+  </si>
+  <si>
+    <t>C70939</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[ANDROID]-Domestic_Payment</t>
+  </si>
+  <si>
+    <t>C70940</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Arhive_Resubmit_Payments_From_Past_Payment_List_[ANDROID]-Prenesi</t>
+  </si>
+  <si>
+    <t>C70941</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Transaction_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70942</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[MOB_ANDROID]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70943</t>
   </si>
   <si>
     <t>Name</t>
@@ -1762,7 +1838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1808,7 +1884,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
@@ -2157,10 +2232,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="112.574074074074" customWidth="1"/>
+    <col min="2" max="2" width="123.185185185185" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2206,8 +2281,9 @@
       <c r="F2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>13</v>
+      <c r="G2" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B2,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="1:7">
@@ -2215,11 +2291,11 @@
         <v>7</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" s="15" t="s">
         <v>10</v>
       </c>
@@ -2229,8 +2305,9 @@
       <c r="F3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="15" t="s">
-        <v>13</v>
+      <c r="G3" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B3,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:7">
@@ -2238,11 +2315,11 @@
         <v>7</v>
       </c>
       <c r="B4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" s="15" t="s">
         <v>10</v>
       </c>
@@ -2252,8 +2329,9 @@
       <c r="F4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="15" t="s">
-        <v>13</v>
+      <c r="G4" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B4,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:7">
@@ -2261,11 +2339,11 @@
         <v>7</v>
       </c>
       <c r="B5" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="15" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" s="15" t="s">
         <v>10</v>
       </c>
@@ -2275,8 +2353,9 @@
       <c r="F5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>13</v>
+      <c r="G5" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B5,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -2284,11 +2363,11 @@
         <v>7</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>21</v>
-      </c>
       <c r="D6" s="15" t="s">
         <v>10</v>
       </c>
@@ -2298,8 +2377,9 @@
       <c r="F6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="15" t="s">
-        <v>13</v>
+      <c r="G6" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B6,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -2307,11 +2387,11 @@
         <v>7</v>
       </c>
       <c r="B7" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>23</v>
-      </c>
       <c r="D7" s="15" t="s">
         <v>10</v>
       </c>
@@ -2321,8 +2401,9 @@
       <c r="F7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="15" t="s">
-        <v>13</v>
+      <c r="G7" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B7,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -2330,11 +2411,11 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>25</v>
-      </c>
       <c r="D8" s="15" t="s">
         <v>10</v>
       </c>
@@ -2344,8 +2425,9 @@
       <c r="F8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="15" t="s">
-        <v>13</v>
+      <c r="G8" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B8,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:7">
@@ -2353,11 +2435,11 @@
         <v>7</v>
       </c>
       <c r="B9" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>27</v>
-      </c>
       <c r="D9" s="15" t="s">
         <v>10</v>
       </c>
@@ -2367,8 +2449,9 @@
       <c r="F9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="15" t="s">
-        <v>13</v>
+      <c r="G9" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B9,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:7">
@@ -2376,11 +2459,11 @@
         <v>7</v>
       </c>
       <c r="B10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>29</v>
-      </c>
       <c r="D10" s="15" t="s">
         <v>10</v>
       </c>
@@ -2390,8 +2473,9 @@
       <c r="F10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="15" t="s">
-        <v>13</v>
+      <c r="G10" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B10,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:7">
@@ -2399,11 +2483,11 @@
         <v>7</v>
       </c>
       <c r="B11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>31</v>
-      </c>
       <c r="D11" s="15" t="s">
         <v>10</v>
       </c>
@@ -2413,8 +2497,9 @@
       <c r="F11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>13</v>
+      <c r="G11" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B11,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:7">
@@ -2422,11 +2507,11 @@
         <v>7</v>
       </c>
       <c r="B12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>33</v>
-      </c>
       <c r="D12" s="15" t="s">
         <v>10</v>
       </c>
@@ -2436,8 +2521,9 @@
       <c r="F12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="15" t="s">
-        <v>13</v>
+      <c r="G12" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B12,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:7">
@@ -2445,11 +2531,11 @@
         <v>7</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>35</v>
-      </c>
       <c r="D13" s="15" t="s">
         <v>10</v>
       </c>
@@ -2459,8 +2545,9 @@
       <c r="F13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="15" t="s">
-        <v>13</v>
+      <c r="G13" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B13,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:7">
@@ -2468,11 +2555,11 @@
         <v>7</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="15" t="s">
-        <v>37</v>
-      </c>
       <c r="D14" s="15" t="s">
         <v>10</v>
       </c>
@@ -2482,8 +2569,9 @@
       <c r="F14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="15" t="s">
-        <v>13</v>
+      <c r="G14" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B14,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:7">
@@ -2491,11 +2579,11 @@
         <v>7</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="15" t="s">
-        <v>39</v>
-      </c>
       <c r="D15" s="15" t="s">
         <v>10</v>
       </c>
@@ -2505,8 +2593,9 @@
       <c r="F15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>13</v>
+      <c r="G15" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B15,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:7">
@@ -2514,11 +2603,11 @@
         <v>7</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="15" t="s">
-        <v>41</v>
-      </c>
       <c r="D16" s="15" t="s">
         <v>10</v>
       </c>
@@ -2528,8 +2617,9 @@
       <c r="F16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="15" t="s">
-        <v>13</v>
+      <c r="G16" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B16,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:7">
@@ -2537,11 +2627,11 @@
         <v>7</v>
       </c>
       <c r="B17" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>43</v>
-      </c>
       <c r="D17" s="15" t="s">
         <v>10</v>
       </c>
@@ -2551,8 +2641,9 @@
       <c r="F17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="15" t="s">
-        <v>13</v>
+      <c r="G17" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B17,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:7">
@@ -2560,11 +2651,11 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C18" s="15" t="s">
-        <v>45</v>
-      </c>
       <c r="D18" s="15" t="s">
         <v>10</v>
       </c>
@@ -2574,8 +2665,9 @@
       <c r="F18" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="15" t="s">
-        <v>13</v>
+      <c r="G18" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B18,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:7">
@@ -2583,11 +2675,11 @@
         <v>7</v>
       </c>
       <c r="B19" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>47</v>
-      </c>
       <c r="D19" s="15" t="s">
         <v>10</v>
       </c>
@@ -2597,8 +2689,9 @@
       <c r="F19" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="15" t="s">
-        <v>13</v>
+      <c r="G19" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B19,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:7">
@@ -2606,11 +2699,11 @@
         <v>7</v>
       </c>
       <c r="B20" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="15" t="s">
-        <v>49</v>
-      </c>
       <c r="D20" s="15" t="s">
         <v>10</v>
       </c>
@@ -2620,8 +2713,9 @@
       <c r="F20" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>13</v>
+      <c r="G20" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B20,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:7">
@@ -2629,11 +2723,11 @@
         <v>7</v>
       </c>
       <c r="B21" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>51</v>
-      </c>
       <c r="D21" s="15" t="s">
         <v>10</v>
       </c>
@@ -2643,8 +2737,9 @@
       <c r="F21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="15" t="s">
-        <v>13</v>
+      <c r="G21" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B21,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:7">
@@ -2652,11 +2747,11 @@
         <v>7</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>53</v>
-      </c>
       <c r="D22" s="15" t="s">
         <v>10</v>
       </c>
@@ -2666,8 +2761,9 @@
       <c r="F22" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="15" t="s">
-        <v>13</v>
+      <c r="G22" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B22,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:7">
@@ -2675,11 +2771,11 @@
         <v>7</v>
       </c>
       <c r="B23" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>55</v>
-      </c>
       <c r="D23" s="15" t="s">
         <v>10</v>
       </c>
@@ -2689,8 +2785,9 @@
       <c r="F23" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="15" t="s">
-        <v>13</v>
+      <c r="G23" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B23,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:7">
@@ -2698,11 +2795,11 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="D24" s="15" t="s">
         <v>10</v>
       </c>
@@ -2712,8 +2809,9 @@
       <c r="F24" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="15" t="s">
-        <v>13</v>
+      <c r="G24" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B24,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:7">
@@ -2721,11 +2819,11 @@
         <v>7</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C25" s="15" t="s">
-        <v>59</v>
-      </c>
       <c r="D25" s="15" t="s">
         <v>10</v>
       </c>
@@ -2735,8 +2833,9 @@
       <c r="F25" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="15" t="s">
-        <v>13</v>
+      <c r="G25" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B25,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:7">
@@ -2744,11 +2843,11 @@
         <v>7</v>
       </c>
       <c r="B26" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>61</v>
-      </c>
       <c r="D26" s="15" t="s">
         <v>10</v>
       </c>
@@ -2758,8 +2857,9 @@
       <c r="F26" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="15" t="s">
-        <v>13</v>
+      <c r="G26" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B26,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:7">
@@ -2767,11 +2867,11 @@
         <v>7</v>
       </c>
       <c r="B27" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>63</v>
-      </c>
       <c r="D27" s="15" t="s">
         <v>10</v>
       </c>
@@ -2781,8 +2881,9 @@
       <c r="F27" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="15" t="s">
-        <v>13</v>
+      <c r="G27" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B27,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:7">
@@ -2790,11 +2891,11 @@
         <v>7</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>65</v>
-      </c>
       <c r="D28" s="15" t="s">
         <v>10</v>
       </c>
@@ -2804,8 +2905,9 @@
       <c r="F28" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="15" t="s">
-        <v>13</v>
+      <c r="G28" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B28,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:7">
@@ -2813,11 +2915,11 @@
         <v>7</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>67</v>
-      </c>
       <c r="D29" s="15" t="s">
         <v>10</v>
       </c>
@@ -2827,8 +2929,9 @@
       <c r="F29" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="15" t="s">
-        <v>13</v>
+      <c r="G29" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B29,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:7">
@@ -2836,11 +2939,11 @@
         <v>7</v>
       </c>
       <c r="B30" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>69</v>
-      </c>
       <c r="D30" s="15" t="s">
         <v>10</v>
       </c>
@@ -2850,8 +2953,9 @@
       <c r="F30" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="15" t="s">
-        <v>13</v>
+      <c r="G30" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B30,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:7">
@@ -2859,11 +2963,11 @@
         <v>7</v>
       </c>
       <c r="B31" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C31" s="15" t="s">
-        <v>71</v>
-      </c>
       <c r="D31" s="15" t="s">
         <v>10</v>
       </c>
@@ -2873,8 +2977,9 @@
       <c r="F31" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="15" t="s">
-        <v>13</v>
+      <c r="G31" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B31,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:7">
@@ -2882,11 +2987,11 @@
         <v>7</v>
       </c>
       <c r="B32" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>73</v>
-      </c>
       <c r="D32" s="15" t="s">
         <v>10</v>
       </c>
@@ -2896,8 +3001,9 @@
       <c r="F32" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="15" t="s">
-        <v>13</v>
+      <c r="G32" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B32,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:7">
@@ -2905,11 +3011,11 @@
         <v>7</v>
       </c>
       <c r="B33" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="15" t="s">
-        <v>75</v>
-      </c>
       <c r="D33" s="15" t="s">
         <v>10</v>
       </c>
@@ -2919,8 +3025,9 @@
       <c r="F33" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="15" t="s">
-        <v>13</v>
+      <c r="G33" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B33,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:7">
@@ -2928,11 +3035,11 @@
         <v>7</v>
       </c>
       <c r="B34" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="15" t="s">
-        <v>77</v>
-      </c>
       <c r="D34" s="15" t="s">
         <v>10</v>
       </c>
@@ -2942,8 +3049,9 @@
       <c r="F34" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="15" t="s">
-        <v>13</v>
+      <c r="G34" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B34,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:7">
@@ -2951,11 +3059,11 @@
         <v>7</v>
       </c>
       <c r="B35" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>79</v>
-      </c>
       <c r="D35" s="15" t="s">
         <v>10</v>
       </c>
@@ -2965,8 +3073,9 @@
       <c r="F35" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="15" t="s">
-        <v>13</v>
+      <c r="G35" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B35,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:7">
@@ -2974,11 +3083,11 @@
         <v>7</v>
       </c>
       <c r="B36" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="15" t="s">
-        <v>81</v>
-      </c>
       <c r="D36" s="15" t="s">
         <v>10</v>
       </c>
@@ -2988,8 +3097,9 @@
       <c r="F36" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="15" t="s">
-        <v>13</v>
+      <c r="G36" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B36,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:7">
@@ -2997,11 +3107,11 @@
         <v>7</v>
       </c>
       <c r="B37" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="15" t="s">
-        <v>83</v>
-      </c>
       <c r="D37" s="15" t="s">
         <v>10</v>
       </c>
@@ -3011,8 +3121,9 @@
       <c r="F37" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="15" t="s">
-        <v>13</v>
+      <c r="G37" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B37,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:7">
@@ -3020,11 +3131,11 @@
         <v>7</v>
       </c>
       <c r="B38" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="15" t="s">
-        <v>85</v>
-      </c>
       <c r="D38" s="15" t="s">
         <v>10</v>
       </c>
@@ -3034,8 +3145,9 @@
       <c r="F38" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="15" t="s">
-        <v>13</v>
+      <c r="G38" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B38,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:7">
@@ -3043,11 +3155,11 @@
         <v>7</v>
       </c>
       <c r="B39" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="15" t="s">
-        <v>87</v>
-      </c>
       <c r="D39" s="15" t="s">
         <v>10</v>
       </c>
@@ -3057,8 +3169,9 @@
       <c r="F39" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="15" t="s">
-        <v>13</v>
+      <c r="G39" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B39,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:7">
@@ -3066,11 +3179,11 @@
         <v>7</v>
       </c>
       <c r="B40" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="15" t="s">
-        <v>89</v>
-      </c>
       <c r="D40" s="15" t="s">
         <v>10</v>
       </c>
@@ -3080,8 +3193,9 @@
       <c r="F40" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="15" t="s">
-        <v>13</v>
+      <c r="G40" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B40,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:7">
@@ -3089,11 +3203,11 @@
         <v>7</v>
       </c>
       <c r="B41" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="15" t="s">
-        <v>91</v>
-      </c>
       <c r="D41" s="15" t="s">
         <v>10</v>
       </c>
@@ -3103,8 +3217,9 @@
       <c r="F41" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="15" t="s">
-        <v>13</v>
+      <c r="G41" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B41,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
@@ -3112,11 +3227,11 @@
         <v>7</v>
       </c>
       <c r="B42" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C42" s="15" t="s">
-        <v>93</v>
-      </c>
       <c r="D42" s="15" t="s">
         <v>10</v>
       </c>
@@ -3126,8 +3241,9 @@
       <c r="F42" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="15" t="s">
-        <v>13</v>
+      <c r="G42" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B42,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:7">
@@ -3135,11 +3251,11 @@
         <v>7</v>
       </c>
       <c r="B43" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="C43" s="15" t="s">
-        <v>95</v>
-      </c>
       <c r="D43" s="15" t="s">
         <v>10</v>
       </c>
@@ -3149,8 +3265,9 @@
       <c r="F43" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="15" t="s">
-        <v>13</v>
+      <c r="G43" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B43,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:7">
@@ -3158,11 +3275,11 @@
         <v>7</v>
       </c>
       <c r="B44" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C44" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C44" s="15" t="s">
-        <v>97</v>
-      </c>
       <c r="D44" s="15" t="s">
         <v>10</v>
       </c>
@@ -3172,8 +3289,9 @@
       <c r="F44" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="15" t="s">
-        <v>13</v>
+      <c r="G44" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B44,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:7">
@@ -3181,11 +3299,11 @@
         <v>7</v>
       </c>
       <c r="B45" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C45" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="15" t="s">
-        <v>99</v>
-      </c>
       <c r="D45" s="15" t="s">
         <v>10</v>
       </c>
@@ -3195,8 +3313,9 @@
       <c r="F45" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="15" t="s">
-        <v>13</v>
+      <c r="G45" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B45,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:7">
@@ -3204,11 +3323,11 @@
         <v>7</v>
       </c>
       <c r="B46" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="15" t="s">
-        <v>101</v>
-      </c>
       <c r="D46" s="15" t="s">
         <v>10</v>
       </c>
@@ -3218,8 +3337,9 @@
       <c r="F46" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="15" t="s">
-        <v>13</v>
+      <c r="G46" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B46,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:7">
@@ -3227,11 +3347,11 @@
         <v>7</v>
       </c>
       <c r="B47" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C47" s="15" t="s">
-        <v>103</v>
-      </c>
       <c r="D47" s="15" t="s">
         <v>10</v>
       </c>
@@ -3241,8 +3361,9 @@
       <c r="F47" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="15" t="s">
-        <v>13</v>
+      <c r="G47" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B47,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:7">
@@ -3250,11 +3371,11 @@
         <v>7</v>
       </c>
       <c r="B48" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C48" s="15" t="s">
-        <v>105</v>
-      </c>
       <c r="D48" s="15" t="s">
         <v>10</v>
       </c>
@@ -3264,8 +3385,9 @@
       <c r="F48" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="15" t="s">
-        <v>13</v>
+      <c r="G48" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B48,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:7">
@@ -3273,11 +3395,11 @@
         <v>7</v>
       </c>
       <c r="B49" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="15" t="s">
-        <v>107</v>
-      </c>
       <c r="D49" s="15" t="s">
         <v>10</v>
       </c>
@@ -3287,8 +3409,9 @@
       <c r="F49" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="15" t="s">
-        <v>13</v>
+      <c r="G49" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B49,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:7">
@@ -3296,11 +3419,11 @@
         <v>7</v>
       </c>
       <c r="B50" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>109</v>
-      </c>
       <c r="D50" s="15" t="s">
         <v>10</v>
       </c>
@@ -3310,8 +3433,9 @@
       <c r="F50" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="15" t="s">
-        <v>13</v>
+      <c r="G50" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B50,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:7">
@@ -3319,11 +3443,11 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C51" s="15" t="s">
-        <v>111</v>
-      </c>
       <c r="D51" s="15" t="s">
         <v>10</v>
       </c>
@@ -3333,8 +3457,9 @@
       <c r="F51" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="15" t="s">
-        <v>13</v>
+      <c r="G51" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B51,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:7">
@@ -3342,11 +3467,11 @@
         <v>7</v>
       </c>
       <c r="B52" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C52" s="15" t="s">
-        <v>113</v>
-      </c>
       <c r="D52" s="15" t="s">
         <v>10</v>
       </c>
@@ -3356,8 +3481,9 @@
       <c r="F52" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="15" t="s">
-        <v>13</v>
+      <c r="G52" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B52,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -3365,11 +3491,11 @@
         <v>7</v>
       </c>
       <c r="B53" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="15" t="s">
-        <v>115</v>
-      </c>
       <c r="D53" s="15" t="s">
         <v>10</v>
       </c>
@@ -3379,8 +3505,9 @@
       <c r="F53" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="15" t="s">
-        <v>13</v>
+      <c r="G53" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B53,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -3388,11 +3515,11 @@
         <v>7</v>
       </c>
       <c r="B54" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C54" s="15" t="s">
-        <v>117</v>
-      </c>
       <c r="D54" s="15" t="s">
         <v>10</v>
       </c>
@@ -3402,8 +3529,9 @@
       <c r="F54" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="15" t="s">
-        <v>13</v>
+      <c r="G54" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B54,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -3411,11 +3539,11 @@
         <v>7</v>
       </c>
       <c r="B55" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="C55" s="15" t="s">
-        <v>119</v>
-      </c>
       <c r="D55" s="15" t="s">
         <v>10</v>
       </c>
@@ -3425,8 +3553,9 @@
       <c r="F55" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="15" t="s">
-        <v>13</v>
+      <c r="G55" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B55,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:7">
@@ -3434,11 +3563,11 @@
         <v>7</v>
       </c>
       <c r="B56" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="15" t="s">
-        <v>121</v>
-      </c>
       <c r="D56" s="15" t="s">
         <v>10</v>
       </c>
@@ -3448,8 +3577,9 @@
       <c r="F56" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="15" t="s">
-        <v>13</v>
+      <c r="G56" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B56,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:7">
@@ -3457,11 +3587,11 @@
         <v>7</v>
       </c>
       <c r="B57" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C57" s="15" t="s">
-        <v>123</v>
-      </c>
       <c r="D57" s="15" t="s">
         <v>10</v>
       </c>
@@ -3471,8 +3601,9 @@
       <c r="F57" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="15" t="s">
-        <v>13</v>
+      <c r="G57" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B57,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:7">
@@ -3480,11 +3611,11 @@
         <v>7</v>
       </c>
       <c r="B58" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C58" s="15" t="s">
-        <v>125</v>
-      </c>
       <c r="D58" s="15" t="s">
         <v>10</v>
       </c>
@@ -3494,8 +3625,9 @@
       <c r="F58" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="15" t="s">
-        <v>13</v>
+      <c r="G58" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B58,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
@@ -3503,11 +3635,11 @@
         <v>7</v>
       </c>
       <c r="B59" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C59" s="15" t="s">
-        <v>127</v>
-      </c>
       <c r="D59" s="15" t="s">
         <v>10</v>
       </c>
@@ -3517,8 +3649,9 @@
       <c r="F59" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="15" t="s">
-        <v>13</v>
+      <c r="G59" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B59,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -3526,11 +3659,11 @@
         <v>7</v>
       </c>
       <c r="B60" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="15" t="s">
-        <v>129</v>
-      </c>
       <c r="D60" s="15" t="s">
         <v>10</v>
       </c>
@@ -3540,8 +3673,9 @@
       <c r="F60" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="15" t="s">
-        <v>13</v>
+      <c r="G60" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B60,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:7">
@@ -3549,11 +3683,11 @@
         <v>7</v>
       </c>
       <c r="B61" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="C61" s="15" t="s">
-        <v>131</v>
-      </c>
       <c r="D61" s="15" t="s">
         <v>10</v>
       </c>
@@ -3563,8 +3697,9 @@
       <c r="F61" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G61" s="15" t="s">
-        <v>13</v>
+      <c r="G61" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B61,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:7">
@@ -3572,11 +3707,11 @@
         <v>7</v>
       </c>
       <c r="B62" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="C62" s="15" t="s">
-        <v>133</v>
-      </c>
       <c r="D62" s="15" t="s">
         <v>10</v>
       </c>
@@ -3586,8 +3721,9 @@
       <c r="F62" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="15" t="s">
-        <v>13</v>
+      <c r="G62" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B62,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:7">
@@ -3595,11 +3731,11 @@
         <v>7</v>
       </c>
       <c r="B63" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="C63" s="15" t="s">
-        <v>135</v>
-      </c>
       <c r="D63" s="15" t="s">
         <v>10</v>
       </c>
@@ -3609,8 +3745,9 @@
       <c r="F63" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="15" t="s">
-        <v>13</v>
+      <c r="G63" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B63,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:7">
@@ -3618,11 +3755,11 @@
         <v>7</v>
       </c>
       <c r="B64" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C64" s="15" t="s">
-        <v>137</v>
-      </c>
       <c r="D64" s="15" t="s">
         <v>10</v>
       </c>
@@ -3632,8 +3769,9 @@
       <c r="F64" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="15" t="s">
-        <v>13</v>
+      <c r="G64" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B64,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:7">
@@ -3641,11 +3779,11 @@
         <v>7</v>
       </c>
       <c r="B65" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C65" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C65" s="15" t="s">
-        <v>139</v>
-      </c>
       <c r="D65" s="15" t="s">
         <v>10</v>
       </c>
@@ -3655,8 +3793,9 @@
       <c r="F65" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="15" t="s">
-        <v>13</v>
+      <c r="G65" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B65,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:7">
@@ -3664,11 +3803,11 @@
         <v>7</v>
       </c>
       <c r="B66" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="C66" s="15" t="s">
-        <v>141</v>
-      </c>
       <c r="D66" s="15" t="s">
         <v>10</v>
       </c>
@@ -3678,8 +3817,9 @@
       <c r="F66" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="15" t="s">
-        <v>13</v>
+      <c r="G66" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B66,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:7">
@@ -3687,11 +3827,11 @@
         <v>7</v>
       </c>
       <c r="B67" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C67" s="15" t="s">
-        <v>143</v>
-      </c>
       <c r="D67" s="15" t="s">
         <v>10</v>
       </c>
@@ -3701,8 +3841,9 @@
       <c r="F67" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G67" s="15" t="s">
-        <v>13</v>
+      <c r="G67" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B67,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:7">
@@ -3710,11 +3851,11 @@
         <v>7</v>
       </c>
       <c r="B68" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C68" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="C68" s="15" t="s">
-        <v>145</v>
-      </c>
       <c r="D68" s="15" t="s">
         <v>10</v>
       </c>
@@ -3724,8 +3865,9 @@
       <c r="F68" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="15" t="s">
-        <v>13</v>
+      <c r="G68" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B68,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -3733,11 +3875,11 @@
         <v>7</v>
       </c>
       <c r="B69" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C69" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C69" s="15" t="s">
-        <v>147</v>
-      </c>
       <c r="D69" s="15" t="s">
         <v>10</v>
       </c>
@@ -3747,8 +3889,9 @@
       <c r="F69" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="15" t="s">
-        <v>13</v>
+      <c r="G69" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B69,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -3756,11 +3899,11 @@
         <v>7</v>
       </c>
       <c r="B70" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C70" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="C70" s="15" t="s">
-        <v>149</v>
-      </c>
       <c r="D70" s="15" t="s">
         <v>10</v>
       </c>
@@ -3770,8 +3913,9 @@
       <c r="F70" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="15" t="s">
-        <v>13</v>
+      <c r="G70" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B70,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:7">
@@ -3779,11 +3923,11 @@
         <v>7</v>
       </c>
       <c r="B71" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C71" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="15" t="s">
-        <v>151</v>
-      </c>
       <c r="D71" s="15" t="s">
         <v>10</v>
       </c>
@@ -3793,8 +3937,9 @@
       <c r="F71" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G71" s="15" t="s">
-        <v>13</v>
+      <c r="G71" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B71,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:7">
@@ -3802,11 +3947,11 @@
         <v>7</v>
       </c>
       <c r="B72" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C72" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="C72" s="15" t="s">
-        <v>153</v>
-      </c>
       <c r="D72" s="15" t="s">
         <v>10</v>
       </c>
@@ -3816,8 +3961,9 @@
       <c r="F72" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="15" t="s">
-        <v>13</v>
+      <c r="G72" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B72,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:7">
@@ -3825,11 +3971,11 @@
         <v>7</v>
       </c>
       <c r="B73" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C73" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C73" s="15" t="s">
-        <v>155</v>
-      </c>
       <c r="D73" s="15" t="s">
         <v>10</v>
       </c>
@@ -3839,8 +3985,9 @@
       <c r="F73" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="15" t="s">
-        <v>13</v>
+      <c r="G73" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B73,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:7">
@@ -3848,11 +3995,11 @@
         <v>7</v>
       </c>
       <c r="B74" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C74" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C74" s="15" t="s">
-        <v>157</v>
-      </c>
       <c r="D74" s="15" t="s">
         <v>10</v>
       </c>
@@ -3862,8 +4009,9 @@
       <c r="F74" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="15" t="s">
-        <v>13</v>
+      <c r="G74" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B74,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:7">
@@ -3871,11 +4019,11 @@
         <v>7</v>
       </c>
       <c r="B75" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C75" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C75" s="15" t="s">
-        <v>159</v>
-      </c>
       <c r="D75" s="15" t="s">
         <v>10</v>
       </c>
@@ -3885,8 +4033,9 @@
       <c r="F75" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="15" t="s">
-        <v>13</v>
+      <c r="G75" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B75,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:7">
@@ -3894,11 +4043,11 @@
         <v>7</v>
       </c>
       <c r="B76" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="C76" s="15" t="s">
-        <v>161</v>
-      </c>
       <c r="D76" s="15" t="s">
         <v>10</v>
       </c>
@@ -3908,8 +4057,9 @@
       <c r="F76" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="15" t="s">
-        <v>13</v>
+      <c r="G76" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B76,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:7">
@@ -3917,11 +4067,11 @@
         <v>7</v>
       </c>
       <c r="B77" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C77" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C77" s="15" t="s">
-        <v>163</v>
-      </c>
       <c r="D77" s="15" t="s">
         <v>10</v>
       </c>
@@ -3931,8 +4081,9 @@
       <c r="F77" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="15" t="s">
-        <v>13</v>
+      <c r="G77" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B77,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:7">
@@ -3940,11 +4091,11 @@
         <v>7</v>
       </c>
       <c r="B78" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C78" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C78" s="15" t="s">
-        <v>165</v>
-      </c>
       <c r="D78" s="15" t="s">
         <v>10</v>
       </c>
@@ -3954,8 +4105,9 @@
       <c r="F78" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="15" t="s">
-        <v>13</v>
+      <c r="G78" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B78,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:7">
@@ -3963,11 +4115,11 @@
         <v>7</v>
       </c>
       <c r="B79" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="C79" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="C79" s="15" t="s">
-        <v>167</v>
-      </c>
       <c r="D79" s="15" t="s">
         <v>10</v>
       </c>
@@ -3977,8 +4129,9 @@
       <c r="F79" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="15" t="s">
-        <v>13</v>
+      <c r="G79" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B79,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:7">
@@ -3986,11 +4139,11 @@
         <v>7</v>
       </c>
       <c r="B80" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C80" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C80" s="15" t="s">
-        <v>169</v>
-      </c>
       <c r="D80" s="15" t="s">
         <v>10</v>
       </c>
@@ -4000,8 +4153,9 @@
       <c r="F80" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="15" t="s">
-        <v>13</v>
+      <c r="G80" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B80,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:7">
@@ -4009,11 +4163,11 @@
         <v>7</v>
       </c>
       <c r="B81" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C81" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="C81" s="15" t="s">
-        <v>171</v>
-      </c>
       <c r="D81" s="15" t="s">
         <v>10</v>
       </c>
@@ -4023,8 +4177,9 @@
       <c r="F81" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G81" s="15" t="s">
-        <v>13</v>
+      <c r="G81" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B81,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -4032,11 +4187,11 @@
         <v>7</v>
       </c>
       <c r="B82" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C82" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C82" s="15" t="s">
-        <v>173</v>
-      </c>
       <c r="D82" s="15" t="s">
         <v>10</v>
       </c>
@@ -4046,8 +4201,9 @@
       <c r="F82" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="15" t="s">
-        <v>13</v>
+      <c r="G82" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B82,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -4055,11 +4211,11 @@
         <v>7</v>
       </c>
       <c r="B83" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="C83" s="15" t="s">
-        <v>175</v>
-      </c>
       <c r="D83" s="15" t="s">
         <v>10</v>
       </c>
@@ -4069,8 +4225,9 @@
       <c r="F83" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="15" t="s">
-        <v>13</v>
+      <c r="G83" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B83,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -4078,11 +4235,11 @@
         <v>7</v>
       </c>
       <c r="B84" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C84" s="15" t="s">
-        <v>177</v>
-      </c>
       <c r="D84" s="15" t="s">
         <v>10</v>
       </c>
@@ -4092,8 +4249,9 @@
       <c r="F84" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G84" s="15" t="s">
-        <v>13</v>
+      <c r="G84" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B84,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:7">
@@ -4101,11 +4259,11 @@
         <v>7</v>
       </c>
       <c r="B85" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="C85" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="C85" s="15" t="s">
-        <v>179</v>
-      </c>
       <c r="D85" s="15" t="s">
         <v>10</v>
       </c>
@@ -4115,8 +4273,9 @@
       <c r="F85" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="15" t="s">
-        <v>13</v>
+      <c r="G85" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B85,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:7">
@@ -4124,11 +4283,11 @@
         <v>7</v>
       </c>
       <c r="B86" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C86" s="15" t="s">
-        <v>181</v>
-      </c>
       <c r="D86" s="15" t="s">
         <v>10</v>
       </c>
@@ -4138,8 +4297,9 @@
       <c r="F86" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="15" t="s">
-        <v>13</v>
+      <c r="G86" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B86,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:7">
@@ -4147,11 +4307,11 @@
         <v>7</v>
       </c>
       <c r="B87" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="C87" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C87" s="15" t="s">
-        <v>183</v>
-      </c>
       <c r="D87" s="15" t="s">
         <v>10</v>
       </c>
@@ -4161,8 +4321,9 @@
       <c r="F87" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G87" s="15" t="s">
-        <v>13</v>
+      <c r="G87" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B87,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:7">
@@ -4170,11 +4331,11 @@
         <v>7</v>
       </c>
       <c r="B88" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="C88" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C88" s="15" t="s">
-        <v>185</v>
-      </c>
       <c r="D88" s="15" t="s">
         <v>10</v>
       </c>
@@ -4184,8 +4345,9 @@
       <c r="F88" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="15" t="s">
-        <v>13</v>
+      <c r="G88" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B88,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:7">
@@ -4193,11 +4355,11 @@
         <v>7</v>
       </c>
       <c r="B89" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="C89" s="15" t="s">
-        <v>187</v>
-      </c>
       <c r="D89" s="15" t="s">
         <v>10</v>
       </c>
@@ -4207,8 +4369,9 @@
       <c r="F89" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="15" t="s">
-        <v>13</v>
+      <c r="G89" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B89,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:7">
@@ -4216,11 +4379,11 @@
         <v>7</v>
       </c>
       <c r="B90" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C90" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C90" s="15" t="s">
-        <v>189</v>
-      </c>
       <c r="D90" s="15" t="s">
         <v>10</v>
       </c>
@@ -4230,8 +4393,9 @@
       <c r="F90" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G90" s="15" t="s">
-        <v>13</v>
+      <c r="G90" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B90,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:7">
@@ -4239,11 +4403,11 @@
         <v>7</v>
       </c>
       <c r="B91" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="C91" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="C91" s="15" t="s">
-        <v>191</v>
-      </c>
       <c r="D91" s="15" t="s">
         <v>10</v>
       </c>
@@ -4253,8 +4417,9 @@
       <c r="F91" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G91" s="15" t="s">
-        <v>13</v>
+      <c r="G91" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B91,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:7">
@@ -4262,11 +4427,11 @@
         <v>7</v>
       </c>
       <c r="B92" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C92" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="C92" s="15" t="s">
-        <v>193</v>
-      </c>
       <c r="D92" s="15" t="s">
         <v>10</v>
       </c>
@@ -4276,8 +4441,9 @@
       <c r="F92" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="15" t="s">
-        <v>13</v>
+      <c r="G92" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B92,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:7">
@@ -4285,11 +4451,11 @@
         <v>7</v>
       </c>
       <c r="B93" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="C93" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C93" s="15" t="s">
-        <v>195</v>
-      </c>
       <c r="D93" s="15" t="s">
         <v>10</v>
       </c>
@@ -4299,8 +4465,9 @@
       <c r="F93" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G93" s="15" t="s">
-        <v>13</v>
+      <c r="G93" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B93,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -4308,11 +4475,11 @@
         <v>7</v>
       </c>
       <c r="B94" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C94" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C94" s="15" t="s">
-        <v>197</v>
-      </c>
       <c r="D94" s="15" t="s">
         <v>10</v>
       </c>
@@ -4322,8 +4489,9 @@
       <c r="F94" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G94" s="15" t="s">
-        <v>13</v>
+      <c r="G94" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B94,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:7">
@@ -4331,11 +4499,11 @@
         <v>7</v>
       </c>
       <c r="B95" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="C95" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="C95" s="15" t="s">
-        <v>199</v>
-      </c>
       <c r="D95" s="15" t="s">
         <v>10</v>
       </c>
@@ -4345,8 +4513,9 @@
       <c r="F95" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="15" t="s">
-        <v>13</v>
+      <c r="G95" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B95,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:7">
@@ -4354,11 +4523,11 @@
         <v>7</v>
       </c>
       <c r="B96" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C96" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="C96" s="15" t="s">
-        <v>201</v>
-      </c>
       <c r="D96" s="15" t="s">
         <v>10</v>
       </c>
@@ -4368,8 +4537,9 @@
       <c r="F96" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G96" s="15" t="s">
-        <v>13</v>
+      <c r="G96" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B96,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:7">
@@ -4377,11 +4547,11 @@
         <v>7</v>
       </c>
       <c r="B97" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C97" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="C97" s="15" t="s">
-        <v>203</v>
-      </c>
       <c r="D97" s="15" t="s">
         <v>10</v>
       </c>
@@ -4391,8 +4561,9 @@
       <c r="F97" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G97" s="15" t="s">
-        <v>13</v>
+      <c r="G97" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B97,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:7">
@@ -4400,11 +4571,11 @@
         <v>7</v>
       </c>
       <c r="B98" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C98" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C98" s="15" t="s">
-        <v>205</v>
-      </c>
       <c r="D98" s="15" t="s">
         <v>10</v>
       </c>
@@ -4414,8 +4585,9 @@
       <c r="F98" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G98" s="15" t="s">
-        <v>13</v>
+      <c r="G98" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B98,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:7">
@@ -4423,11 +4595,11 @@
         <v>7</v>
       </c>
       <c r="B99" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C99" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="C99" s="15" t="s">
-        <v>207</v>
-      </c>
       <c r="D99" s="15" t="s">
         <v>10</v>
       </c>
@@ -4437,8 +4609,9 @@
       <c r="F99" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="15" t="s">
-        <v>13</v>
+      <c r="G99" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B99,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:7">
@@ -4446,11 +4619,11 @@
         <v>7</v>
       </c>
       <c r="B100" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C100" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="C100" s="15" t="s">
-        <v>209</v>
-      </c>
       <c r="D100" s="15" t="s">
         <v>10</v>
       </c>
@@ -4460,8 +4633,9 @@
       <c r="F100" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G100" s="15" t="s">
-        <v>13</v>
+      <c r="G100" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B100,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:7">
@@ -4469,11 +4643,11 @@
         <v>7</v>
       </c>
       <c r="B101" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="C101" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="C101" s="15" t="s">
-        <v>211</v>
-      </c>
       <c r="D101" s="15" t="s">
         <v>10</v>
       </c>
@@ -4483,8 +4657,9 @@
       <c r="F101" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G101" s="15" t="s">
-        <v>13</v>
+      <c r="G101" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B101,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:7">
@@ -4492,11 +4667,11 @@
         <v>7</v>
       </c>
       <c r="B102" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C102" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C102" s="15" t="s">
-        <v>213</v>
-      </c>
       <c r="D102" s="15" t="s">
         <v>10</v>
       </c>
@@ -4506,8 +4681,9 @@
       <c r="F102" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="15" t="s">
-        <v>13</v>
+      <c r="G102" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B102,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:7">
@@ -4515,11 +4691,11 @@
         <v>7</v>
       </c>
       <c r="B103" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C103" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="C103" s="15" t="s">
-        <v>215</v>
-      </c>
       <c r="D103" s="15" t="s">
         <v>10</v>
       </c>
@@ -4529,8 +4705,9 @@
       <c r="F103" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G103" s="15" t="s">
-        <v>13</v>
+      <c r="G103" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B103,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -4538,11 +4715,11 @@
         <v>7</v>
       </c>
       <c r="B104" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C104" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C104" s="15" t="s">
-        <v>217</v>
-      </c>
       <c r="D104" s="15" t="s">
         <v>10</v>
       </c>
@@ -4552,8 +4729,9 @@
       <c r="F104" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G104" s="15" t="s">
-        <v>13</v>
+      <c r="G104" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B104,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -4561,11 +4739,11 @@
         <v>7</v>
       </c>
       <c r="B105" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C105" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C105" s="15" t="s">
-        <v>219</v>
-      </c>
       <c r="D105" s="15" t="s">
         <v>10</v>
       </c>
@@ -4575,8 +4753,9 @@
       <c r="F105" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G105" s="15" t="s">
-        <v>13</v>
+      <c r="G105" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B105,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:7">
@@ -4584,11 +4763,11 @@
         <v>7</v>
       </c>
       <c r="B106" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C106" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C106" s="15" t="s">
-        <v>221</v>
-      </c>
       <c r="D106" s="15" t="s">
         <v>10</v>
       </c>
@@ -4598,8 +4777,9 @@
       <c r="F106" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G106" s="15" t="s">
-        <v>13</v>
+      <c r="G106" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B106,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:7">
@@ -4607,11 +4787,11 @@
         <v>7</v>
       </c>
       <c r="B107" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C107" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C107" s="15" t="s">
-        <v>223</v>
-      </c>
       <c r="D107" s="15" t="s">
         <v>10</v>
       </c>
@@ -4621,8 +4801,9 @@
       <c r="F107" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G107" s="15" t="s">
-        <v>13</v>
+      <c r="G107" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B107,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:7">
@@ -4630,11 +4811,11 @@
         <v>7</v>
       </c>
       <c r="B108" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C108" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="C108" s="15" t="s">
-        <v>225</v>
-      </c>
       <c r="D108" s="15" t="s">
         <v>10</v>
       </c>
@@ -4644,8 +4825,9 @@
       <c r="F108" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G108" s="15" t="s">
-        <v>13</v>
+      <c r="G108" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B108,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:7">
@@ -4653,11 +4835,11 @@
         <v>7</v>
       </c>
       <c r="B109" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C109" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C109" s="15" t="s">
-        <v>227</v>
-      </c>
       <c r="D109" s="15" t="s">
         <v>10</v>
       </c>
@@ -4667,8 +4849,9 @@
       <c r="F109" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G109" s="15" t="s">
-        <v>13</v>
+      <c r="G109" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B109,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:7">
@@ -4676,11 +4859,11 @@
         <v>7</v>
       </c>
       <c r="B110" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="C110" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="C110" s="15" t="s">
-        <v>229</v>
-      </c>
       <c r="D110" s="15" t="s">
         <v>10</v>
       </c>
@@ -4690,8 +4873,9 @@
       <c r="F110" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G110" s="15" t="s">
-        <v>13</v>
+      <c r="G110" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B110,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:7">
@@ -4699,11 +4883,11 @@
         <v>7</v>
       </c>
       <c r="B111" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C111" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C111" s="15" t="s">
-        <v>231</v>
-      </c>
       <c r="D111" s="15" t="s">
         <v>10</v>
       </c>
@@ -4713,8 +4897,9 @@
       <c r="F111" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G111" s="15" t="s">
-        <v>13</v>
+      <c r="G111" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B111,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:7">
@@ -4722,11 +4907,11 @@
         <v>7</v>
       </c>
       <c r="B112" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C112" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C112" s="15" t="s">
-        <v>233</v>
-      </c>
       <c r="D112" s="15" t="s">
         <v>10</v>
       </c>
@@ -4736,8 +4921,9 @@
       <c r="F112" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="15" t="s">
-        <v>13</v>
+      <c r="G112" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B112,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:7">
@@ -4745,11 +4931,11 @@
         <v>7</v>
       </c>
       <c r="B113" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="C113" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C113" s="15" t="s">
-        <v>235</v>
-      </c>
       <c r="D113" s="15" t="s">
         <v>10</v>
       </c>
@@ -4759,8 +4945,9 @@
       <c r="F113" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G113" s="15" t="s">
-        <v>13</v>
+      <c r="G113" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B113,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:7">
@@ -4768,11 +4955,11 @@
         <v>7</v>
       </c>
       <c r="B114" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C114" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="C114" s="15" t="s">
-        <v>237</v>
-      </c>
       <c r="D114" s="15" t="s">
         <v>10</v>
       </c>
@@ -4782,8 +4969,9 @@
       <c r="F114" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="15" t="s">
-        <v>13</v>
+      <c r="G114" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B114,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:7">
@@ -4791,11 +4979,11 @@
         <v>7</v>
       </c>
       <c r="B115" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="C115" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C115" s="15" t="s">
-        <v>239</v>
-      </c>
       <c r="D115" s="15" t="s">
         <v>10</v>
       </c>
@@ -4805,8 +4993,9 @@
       <c r="F115" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="15" t="s">
-        <v>13</v>
+      <c r="G115" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B115,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:7">
@@ -4814,11 +5003,11 @@
         <v>7</v>
       </c>
       <c r="B116" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="C116" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="C116" s="15" t="s">
-        <v>241</v>
-      </c>
       <c r="D116" s="15" t="s">
         <v>10</v>
       </c>
@@ -4828,8 +5017,9 @@
       <c r="F116" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G116" s="15" t="s">
-        <v>13</v>
+      <c r="G116" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B116,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:7">
@@ -4837,11 +5027,11 @@
         <v>7</v>
       </c>
       <c r="B117" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="C117" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C117" s="15" t="s">
-        <v>243</v>
-      </c>
       <c r="D117" s="15" t="s">
         <v>10</v>
       </c>
@@ -4851,8 +5041,9 @@
       <c r="F117" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G117" s="15" t="s">
-        <v>13</v>
+      <c r="G117" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B117,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:7">
@@ -4860,11 +5051,11 @@
         <v>7</v>
       </c>
       <c r="B118" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="C118" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C118" s="15" t="s">
-        <v>245</v>
-      </c>
       <c r="D118" s="15" t="s">
         <v>10</v>
       </c>
@@ -4874,8 +5065,9 @@
       <c r="F118" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G118" s="15" t="s">
-        <v>13</v>
+      <c r="G118" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B118,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:7">
@@ -4883,11 +5075,11 @@
         <v>7</v>
       </c>
       <c r="B119" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C119" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="C119" s="15" t="s">
-        <v>247</v>
-      </c>
       <c r="D119" s="15" t="s">
         <v>10</v>
       </c>
@@ -4897,8 +5089,9 @@
       <c r="F119" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G119" s="15" t="s">
-        <v>13</v>
+      <c r="G119" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B119,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:7">
@@ -4906,11 +5099,11 @@
         <v>7</v>
       </c>
       <c r="B120" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C120" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C120" s="15" t="s">
-        <v>249</v>
-      </c>
       <c r="D120" s="15" t="s">
         <v>10</v>
       </c>
@@ -4920,8 +5113,9 @@
       <c r="F120" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G120" s="15" t="s">
-        <v>13</v>
+      <c r="G120" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B120,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:7">
@@ -4929,11 +5123,11 @@
         <v>7</v>
       </c>
       <c r="B121" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C121" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C121" s="15" t="s">
-        <v>251</v>
-      </c>
       <c r="D121" s="15" t="s">
         <v>10</v>
       </c>
@@ -4943,8 +5137,9 @@
       <c r="F121" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G121" s="15" t="s">
-        <v>13</v>
+      <c r="G121" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B121,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -4952,11 +5147,11 @@
         <v>7</v>
       </c>
       <c r="B122" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C122" s="15" t="s">
         <v>252</v>
       </c>
-      <c r="C122" s="15" t="s">
-        <v>253</v>
-      </c>
       <c r="D122" s="15" t="s">
         <v>10</v>
       </c>
@@ -4966,8 +5161,9 @@
       <c r="F122" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="15" t="s">
-        <v>13</v>
+      <c r="G122" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B122,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:7">
@@ -4975,11 +5171,11 @@
         <v>7</v>
       </c>
       <c r="B123" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C123" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="C123" s="15" t="s">
-        <v>255</v>
-      </c>
       <c r="D123" s="15" t="s">
         <v>10</v>
       </c>
@@ -4989,8 +5185,9 @@
       <c r="F123" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G123" s="15" t="s">
-        <v>13</v>
+      <c r="G123" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B123,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:7">
@@ -4998,11 +5195,11 @@
         <v>7</v>
       </c>
       <c r="B124" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C124" s="15" t="s">
         <v>256</v>
       </c>
-      <c r="C124" s="15" t="s">
-        <v>257</v>
-      </c>
       <c r="D124" s="15" t="s">
         <v>10</v>
       </c>
@@ -5012,8 +5209,9 @@
       <c r="F124" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="15" t="s">
-        <v>13</v>
+      <c r="G124" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B124,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="125" customFormat="1" spans="1:7">
@@ -5021,11 +5219,11 @@
         <v>7</v>
       </c>
       <c r="B125" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="C125" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C125" s="15" t="s">
-        <v>259</v>
-      </c>
       <c r="D125" s="15" t="s">
         <v>10</v>
       </c>
@@ -5035,8 +5233,9 @@
       <c r="F125" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G125" s="15" t="s">
-        <v>13</v>
+      <c r="G125" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B125,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:7">
@@ -5044,11 +5243,11 @@
         <v>7</v>
       </c>
       <c r="B126" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C126" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C126" s="15" t="s">
-        <v>261</v>
-      </c>
       <c r="D126" s="15" t="s">
         <v>10</v>
       </c>
@@ -5058,8 +5257,9 @@
       <c r="F126" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G126" s="15" t="s">
-        <v>13</v>
+      <c r="G126" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B126,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>off</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -5067,11 +5267,11 @@
         <v>7</v>
       </c>
       <c r="B127" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C127" s="15" t="s">
         <v>262</v>
       </c>
-      <c r="C127" s="15" t="s">
-        <v>263</v>
-      </c>
       <c r="D127" s="15" t="s">
         <v>10</v>
       </c>
@@ -5081,8 +5281,9 @@
       <c r="F127" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G127" s="15" t="s">
-        <v>13</v>
+      <c r="G127" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B127,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="128" customFormat="1" spans="1:7">
@@ -5090,11 +5291,11 @@
         <v>7</v>
       </c>
       <c r="B128" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C128" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="C128" s="15" t="s">
-        <v>265</v>
-      </c>
       <c r="D128" s="15" t="s">
         <v>10</v>
       </c>
@@ -5104,8 +5305,9 @@
       <c r="F128" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="15" t="s">
-        <v>13</v>
+      <c r="G128" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B128,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:7">
@@ -5113,11 +5315,11 @@
         <v>7</v>
       </c>
       <c r="B129" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C129" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C129" s="15" t="s">
-        <v>267</v>
-      </c>
       <c r="D129" s="15" t="s">
         <v>10</v>
       </c>
@@ -5127,8 +5329,9 @@
       <c r="F129" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G129" s="15" t="s">
-        <v>13</v>
+      <c r="G129" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B129,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:7">
@@ -5136,11 +5339,11 @@
         <v>7</v>
       </c>
       <c r="B130" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="C130" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="C130" s="15" t="s">
-        <v>269</v>
-      </c>
       <c r="D130" s="15" t="s">
         <v>10</v>
       </c>
@@ -5150,8 +5353,9 @@
       <c r="F130" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G130" s="15" t="s">
-        <v>13</v>
+      <c r="G130" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B130,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="131" customFormat="1" spans="1:7">
@@ -5159,11 +5363,11 @@
         <v>7</v>
       </c>
       <c r="B131" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C131" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="C131" s="15" t="s">
-        <v>271</v>
-      </c>
       <c r="D131" s="15" t="s">
         <v>10</v>
       </c>
@@ -5173,8 +5377,9 @@
       <c r="F131" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G131" s="15" t="s">
-        <v>13</v>
+      <c r="G131" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B131,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="132" customFormat="1" spans="1:7">
@@ -5182,11 +5387,11 @@
         <v>7</v>
       </c>
       <c r="B132" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C132" s="15" t="s">
         <v>272</v>
       </c>
-      <c r="C132" s="15" t="s">
-        <v>273</v>
-      </c>
       <c r="D132" s="15" t="s">
         <v>10</v>
       </c>
@@ -5196,8 +5401,9 @@
       <c r="F132" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G132" s="15" t="s">
-        <v>13</v>
+      <c r="G132" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B132,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="133" customFormat="1" spans="1:7">
@@ -5205,11 +5411,11 @@
         <v>7</v>
       </c>
       <c r="B133" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C133" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="C133" s="15" t="s">
-        <v>275</v>
-      </c>
       <c r="D133" s="15" t="s">
         <v>10</v>
       </c>
@@ -5219,8 +5425,9 @@
       <c r="F133" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G133" s="15" t="s">
-        <v>13</v>
+      <c r="G133" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B133,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:7">
@@ -5228,11 +5435,11 @@
         <v>7</v>
       </c>
       <c r="B134" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C134" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C134" s="15" t="s">
-        <v>277</v>
-      </c>
       <c r="D134" s="15" t="s">
         <v>10</v>
       </c>
@@ -5242,8 +5449,9 @@
       <c r="F134" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G134" s="15" t="s">
-        <v>13</v>
+      <c r="G134" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B134,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:7">
@@ -5251,22 +5459,23 @@
         <v>7</v>
       </c>
       <c r="B135" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C135" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C135" s="15" t="s">
-        <v>279</v>
-      </c>
       <c r="D135" s="15" t="s">
-        <v>280</v>
+        <v>10</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>281</v>
+        <v>11</v>
       </c>
       <c r="F135" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G135" s="15" t="s">
-        <v>13</v>
+      <c r="G135" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B135,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:7">
@@ -5274,10 +5483,10 @@
         <v>7</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>10</v>
@@ -5288,8 +5497,9 @@
       <c r="F136" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G136" s="15" t="s">
-        <v>13</v>
+      <c r="G136" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B136,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:7">
@@ -5297,10 +5507,10 @@
         <v>7</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D137" s="15" t="s">
         <v>10</v>
@@ -5311,8 +5521,9 @@
       <c r="F137" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G137" s="15" t="s">
-        <v>13</v>
+      <c r="G137" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B137,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:7">
@@ -5320,10 +5531,10 @@
         <v>7</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>10</v>
@@ -5334,8 +5545,9 @@
       <c r="F138" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G138" s="15" t="s">
-        <v>13</v>
+      <c r="G138" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B138,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="139" customFormat="1" spans="1:7">
@@ -5343,10 +5555,10 @@
         <v>7</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D139" s="15" t="s">
         <v>10</v>
@@ -5357,8 +5569,9 @@
       <c r="F139" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G139" s="15" t="s">
-        <v>13</v>
+      <c r="G139" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B139,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="140" customFormat="1" spans="1:7">
@@ -5366,10 +5579,10 @@
         <v>7</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>10</v>
@@ -5380,8 +5593,9 @@
       <c r="F140" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G140" s="15" t="s">
-        <v>13</v>
+      <c r="G140" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B140,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="141" customFormat="1" spans="1:7">
@@ -5389,10 +5603,10 @@
         <v>7</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D141" s="15" t="s">
         <v>10</v>
@@ -5403,8 +5617,9 @@
       <c r="F141" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G141" s="15" t="s">
-        <v>13</v>
+      <c r="G141" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B141,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:7">
@@ -5412,10 +5627,10 @@
         <v>7</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>10</v>
@@ -5426,8 +5641,9 @@
       <c r="F142" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G142" s="15" t="s">
-        <v>13</v>
+      <c r="G142" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B142,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="143" customFormat="1" spans="1:7">
@@ -5435,10 +5651,10 @@
         <v>7</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>10</v>
@@ -5449,8 +5665,9 @@
       <c r="F143" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G143" s="15" t="s">
-        <v>13</v>
+      <c r="G143" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B143,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="144" customFormat="1" spans="1:7">
@@ -5458,10 +5675,10 @@
         <v>7</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>10</v>
@@ -5472,8 +5689,9 @@
       <c r="F144" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G144" s="15" t="s">
-        <v>13</v>
+      <c r="G144" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B144,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="145" customFormat="1" spans="1:7">
@@ -5481,10 +5699,10 @@
         <v>7</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D145" s="15" t="s">
         <v>10</v>
@@ -5495,8 +5713,9 @@
       <c r="F145" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G145" s="15" t="s">
-        <v>13</v>
+      <c r="G145" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B145,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="146" customFormat="1" spans="1:7">
@@ -5504,10 +5723,10 @@
         <v>7</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>10</v>
@@ -5518,8 +5737,9 @@
       <c r="F146" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G146" s="19" t="s">
-        <v>13</v>
+      <c r="G146" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B146,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="147" customFormat="1" spans="1:7">
@@ -5527,10 +5747,10 @@
         <v>7</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D147" s="15" t="s">
         <v>10</v>
@@ -5541,147 +5761,412 @@
       <c r="F147" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G147" s="19" t="s">
-        <v>13</v>
+      <c r="G147" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B147,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
       </c>
     </row>
     <row r="148" customFormat="1" spans="1:7">
       <c r="A148" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B148" s="20" t="s">
+      <c r="B148" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="C148" s="15" t="s">
+        <v>304</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B148,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:7">
+      <c r="A149" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B149" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="C149" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G149" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B149,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:7">
+      <c r="A150" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C150" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C148" s="15" t="s">
+      <c r="D150" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B150,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" spans="1:7">
+      <c r="A151" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B151" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C151" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="D148" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E148" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G148" s="19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="149" customFormat="1" spans="1:7">
-      <c r="A149" s="15"/>
-      <c r="B149" s="15"/>
-      <c r="C149" s="15"/>
-      <c r="D149" s="15"/>
-      <c r="E149" s="15"/>
-      <c r="F149" s="17"/>
-    </row>
-    <row r="150" customFormat="1" spans="1:7">
-      <c r="A150" s="15"/>
-      <c r="B150" s="15"/>
-      <c r="C150" s="15"/>
-      <c r="D150" s="15"/>
-      <c r="E150" s="15"/>
-      <c r="F150" s="17"/>
-    </row>
-    <row r="151" customFormat="1" spans="1:7">
-      <c r="A151" s="15"/>
-      <c r="B151" s="15"/>
-      <c r="C151" s="15"/>
-      <c r="D151" s="15"/>
-      <c r="E151" s="15"/>
-      <c r="F151" s="17"/>
+      <c r="D151" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B151,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
     </row>
     <row r="152" customFormat="1" spans="1:7">
-      <c r="A152" s="15"/>
-      <c r="B152" s="15"/>
-      <c r="C152" s="15"/>
-      <c r="D152" s="15"/>
-      <c r="E152" s="15"/>
-      <c r="F152" s="17"/>
+      <c r="A152" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C152" s="15" t="s">
+        <v>308</v>
+      </c>
+      <c r="D152" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B152,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
     </row>
     <row r="153" customFormat="1" spans="1:7">
-      <c r="A153" s="15"/>
-      <c r="B153" s="15"/>
-      <c r="C153" s="15"/>
-      <c r="D153" s="15"/>
-      <c r="E153" s="15"/>
-      <c r="F153" s="17"/>
+      <c r="A153" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B153" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="C153" s="15" t="s">
+        <v>309</v>
+      </c>
+      <c r="D153" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G153" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B153,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
     </row>
     <row r="154" customFormat="1" spans="1:7">
-      <c r="A154" s="15"/>
-      <c r="B154" s="15"/>
-      <c r="C154" s="15"/>
-      <c r="D154" s="15"/>
-      <c r="E154" s="15"/>
-      <c r="F154" s="17"/>
+      <c r="A154" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C154" s="15" t="s">
+        <v>310</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G154" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B154,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
     </row>
     <row r="155" customFormat="1" spans="1:7">
-      <c r="A155" s="15"/>
-      <c r="B155" s="15"/>
-      <c r="C155" s="15"/>
-      <c r="D155" s="15"/>
-      <c r="E155" s="15"/>
-      <c r="F155" s="17"/>
+      <c r="A155" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B155" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C155" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="D155" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G155" s="15" t="str">
+        <f>IF(ISNUMBER(MATCH(B155,Sheet3!$A:$A,0)),"on","off")</f>
+        <v>on</v>
+      </c>
     </row>
     <row r="156" customFormat="1" spans="1:7">
       <c r="A156" s="15"/>
-      <c r="B156" s="15"/>
-      <c r="C156" s="15"/>
-      <c r="D156" s="15"/>
-      <c r="E156" s="15"/>
-      <c r="F156" s="17"/>
+      <c r="B156" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C156" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="D156" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G156" s="15" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="157" customFormat="1" spans="1:7">
       <c r="A157" s="15"/>
-      <c r="B157" s="15"/>
-      <c r="C157" s="15"/>
-      <c r="D157" s="15"/>
-      <c r="E157" s="15"/>
-      <c r="F157" s="17"/>
+      <c r="B157" s="15" t="s">
+        <v>315</v>
+      </c>
+      <c r="C157" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="D157" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" s="15" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="158" customFormat="1" spans="1:7">
       <c r="A158" s="15"/>
-      <c r="B158" s="15"/>
-      <c r="C158" s="15"/>
-      <c r="D158" s="15"/>
-      <c r="E158" s="15"/>
-      <c r="F158" s="17"/>
+      <c r="B158" s="15" t="s">
+        <v>317</v>
+      </c>
+      <c r="C158" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="D158" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" s="15" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="159" customFormat="1" spans="1:7">
       <c r="A159" s="15"/>
-      <c r="B159" s="15"/>
-      <c r="C159" s="15"/>
-      <c r="D159" s="15"/>
-      <c r="E159" s="15"/>
-      <c r="F159" s="17"/>
+      <c r="B159" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C159" s="15" t="s">
+        <v>320</v>
+      </c>
+      <c r="D159" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G159" s="15" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="160" customFormat="1" spans="1:7">
       <c r="A160" s="15"/>
-      <c r="B160" s="15"/>
-      <c r="C160" s="15"/>
-      <c r="D160" s="15"/>
-      <c r="E160" s="15"/>
-      <c r="F160" s="17"/>
-    </row>
-    <row r="161" customFormat="1" spans="1:6">
+      <c r="B160" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="C160" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="D160" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="161" customFormat="1" spans="1:7">
       <c r="A161" s="15"/>
-      <c r="B161" s="15"/>
-      <c r="C161" s="15"/>
-      <c r="D161" s="15"/>
-      <c r="E161" s="15"/>
-      <c r="F161" s="17"/>
-    </row>
-    <row r="162" customFormat="1" spans="1:6">
+      <c r="B161" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="C161" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="D161" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G161" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="162" customFormat="1" spans="1:7">
       <c r="A162" s="15"/>
-      <c r="B162" s="15"/>
-      <c r="C162" s="15"/>
-      <c r="D162" s="15"/>
-      <c r="E162" s="15"/>
-      <c r="F162" s="17"/>
+      <c r="B162" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C162" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="D162" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E162" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="B163" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="C163" s="15" t="s">
+        <v>328</v>
+      </c>
+      <c r="D163" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E163" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="B164" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="C164" s="15" t="s">
+        <v>330</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E164" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="B165" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="C165" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="D165" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E165" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G165" s="15" t="s">
+        <v>314</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G148" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G164" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B128">
@@ -5743,23 +6228,23 @@
   <conditionalFormatting sqref="B146">
     <cfRule type="duplicateValues" dxfId="2" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C146">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B147">
     <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C147">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B148">
     <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C148">
+  <conditionalFormatting sqref="C1:C127 C133 C166:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C146 C150 C154">
+    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C147 C151 C155:C165">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C148:C150 C152:C153">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C1:C127 C133 C149:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="25"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -5782,297 +6267,297 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>308</v>
+        <v>333</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" ht="77" customHeight="1" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>317</v>
+        <v>342</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>318</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>312</v>
+        <v>337</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:5">
       <c r="A14" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -6082,383 +6567,383 @@
         <v>8</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" s="3" customFormat="1" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
     </row>
     <row r="31" s="3" customFormat="1" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11" t="s">
-        <v>323</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="115.2" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>326</v>
+        <v>351</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="28.8" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>328</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:5">
       <c r="A49" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="100.8" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:5">
       <c r="A60" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:5">
       <c r="A61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:5">
       <c r="A62" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="63" s="3" customFormat="1" spans="1:5">
       <c r="A63" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:5">
       <c r="A64" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -6472,325 +6957,550 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D877"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G877"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="131.333333333333" customWidth="1"/>
+    <col min="2" max="2" width="19.7777777777778" customWidth="1"/>
     <col min="3" max="3" width="10.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.15" spans="1:4">
+    <row r="1" ht="15.15" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="2" ht="15.15" spans="1:4">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="2" ht="15.15" hidden="1" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D2" t="str">
+        <v>15</v>
+      </c>
+      <c r="B2" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A9)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G2" t="str">
         <f>IF(ISNUMBER(MATCH(B2,Sheet3!$A:$A,0)),"on","off")</f>
         <v>off</v>
       </c>
     </row>
-    <row r="3" ht="15.15" spans="1:4">
+    <row r="3" ht="15.15" hidden="1" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="4" ht="15.15" spans="1:4">
+        <v>263</v>
+      </c>
+      <c r="B3" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A10)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="4" ht="15.15" hidden="1" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="5" ht="15.15" spans="1:4">
+        <v>261</v>
+      </c>
+      <c r="B4" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A11)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="5" ht="15.15" hidden="1" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" ht="15.15" spans="1:4">
+        <v>87</v>
+      </c>
+      <c r="B5" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A12)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="6" ht="15.15" hidden="1" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" ht="15.15" spans="1:4">
+        <v>119</v>
+      </c>
+      <c r="B6" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A13)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="7" ht="15.15" hidden="1" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" ht="15.15" spans="1:4">
+        <v>167</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A14)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="8" ht="15.15" hidden="1" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" ht="15.15" spans="1:4">
+        <v>207</v>
+      </c>
+      <c r="B8" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A15)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="9" ht="15.15" hidden="1" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" ht="15.15" spans="1:4">
+        <v>73</v>
+      </c>
+      <c r="B9" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A16)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="10" ht="15.15" hidden="1" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" ht="15.15" spans="1:4">
+        <v>149</v>
+      </c>
+      <c r="B10" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A17)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="11" ht="15.15" hidden="1" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" ht="15.15" spans="1:4">
+        <v>83</v>
+      </c>
+      <c r="B11" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A18)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="12" ht="15.15" hidden="1" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="13" ht="15.15" spans="1:4">
+        <v>265</v>
+      </c>
+      <c r="B12" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A19)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="13" ht="15.15" hidden="1" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14" ht="15.15" spans="1:4">
+        <v>267</v>
+      </c>
+      <c r="B13" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A20)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="14" ht="15.15" hidden="1" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="15" ht="15.15" spans="1:4">
+        <v>177</v>
+      </c>
+      <c r="B14" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A21)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="15" ht="15.15" hidden="1" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="16" ht="15.15" spans="1:4">
+        <v>269</v>
+      </c>
+      <c r="B15" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A22)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="16" ht="15.15" hidden="1" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" ht="15.15" spans="1:1">
+        <v>189</v>
+      </c>
+      <c r="B16" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A23)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="17" ht="15.15" hidden="1" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" ht="15.15" spans="1:1">
+        <v>271</v>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A24)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="18" ht="15.15" hidden="1" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" ht="15.15" spans="1:1">
+        <v>151</v>
+      </c>
+      <c r="B18" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A25)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="19" ht="15.15" hidden="1" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="20" ht="15.15" spans="1:1">
+        <v>181</v>
+      </c>
+      <c r="B19" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A26)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="20" ht="15.15" hidden="1" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="21" ht="15.15" spans="1:1">
+        <v>251</v>
+      </c>
+      <c r="B20" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A27)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="21" ht="15.15" hidden="1" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="22" ht="15.15" spans="1:1">
+        <v>163</v>
+      </c>
+      <c r="B21" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A28)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="22" ht="15.15" hidden="1" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="23" ht="15.15" spans="1:1">
+        <v>285</v>
+      </c>
+      <c r="B22" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A29)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="23" ht="15.15" hidden="1" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="24" ht="15.15" spans="1:1">
+        <v>257</v>
+      </c>
+      <c r="B23" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A30)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="24" ht="15.15" hidden="1" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="25" ht="15.15" spans="1:1">
+        <v>255</v>
+      </c>
+      <c r="B24" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A31)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="25" ht="15.15" hidden="1" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="26" ht="15.15" spans="1:1">
+        <v>273</v>
+      </c>
+      <c r="B25" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A32)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="26" ht="15.15" hidden="1" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="27" ht="15.15" spans="1:1">
+        <v>275</v>
+      </c>
+      <c r="B26" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A33)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="27" ht="15.15" hidden="1" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="28" ht="15.15" spans="1:1">
+        <v>277</v>
+      </c>
+      <c r="B27" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A34)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="28" ht="15.15" hidden="1" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="29" ht="15.15" spans="1:1">
+        <v>299</v>
+      </c>
+      <c r="B28" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A35)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="29" ht="15.15" hidden="1" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="30" ht="15.15" spans="1:1">
+        <v>109</v>
+      </c>
+      <c r="B29" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A36)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="30" ht="15.15" hidden="1" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="31" ht="15.15" spans="1:1">
+        <v>301</v>
+      </c>
+      <c r="B30" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A37)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="31" ht="15.15" hidden="1" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="32" ht="15.15" spans="1:1">
+        <v>303</v>
+      </c>
+      <c r="B31" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A38)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="32" ht="15.15" hidden="1" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="33" ht="15.15" spans="1:1">
+        <v>203</v>
+      </c>
+      <c r="B32" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A39)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="33" ht="15.15" hidden="1" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="34" ht="15.15" spans="1:1">
+        <v>231</v>
+      </c>
+      <c r="B33" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A40)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="34" ht="15.15" hidden="1" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="35" ht="15.15" spans="1:1">
+        <v>229</v>
+      </c>
+      <c r="B34" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A41)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="35" ht="15.15" hidden="1" spans="1:2">
       <c r="A35" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="36" ht="15.15" spans="1:1">
+        <v>233</v>
+      </c>
+      <c r="B35" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A42)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="36" ht="15.15" hidden="1" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="37" ht="15.15" spans="1:1">
+        <v>237</v>
+      </c>
+      <c r="B36" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A43)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="37" ht="15.15" hidden="1" spans="1:2">
       <c r="A37" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="38" ht="15.15" spans="1:1">
+        <v>241</v>
+      </c>
+      <c r="B37" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A44)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="38" ht="15.15" hidden="1" spans="1:2">
       <c r="A38" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="39" ht="15.15" spans="1:1">
+        <v>235</v>
+      </c>
+      <c r="B38" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A45)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="39" ht="15.15" hidden="1" spans="1:2">
       <c r="A39" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="40" ht="15.15" spans="1:1">
+        <v>239</v>
+      </c>
+      <c r="B39" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A46)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="40" ht="15.15" hidden="1" spans="1:2">
       <c r="A40" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="41" ht="15.15" spans="1:1">
+        <v>243</v>
+      </c>
+      <c r="B40" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A47)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="41" ht="15.15" hidden="1" spans="1:2">
       <c r="A41" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="42" ht="15.15" spans="1:1">
+        <v>279</v>
+      </c>
+      <c r="B41" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A48)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="42" ht="15.15" hidden="1" spans="1:2">
       <c r="A42" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="43" ht="15.15" spans="1:1">
+        <v>281</v>
+      </c>
+      <c r="B42" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A49)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="43" ht="15.15" hidden="1" spans="1:2">
       <c r="A43" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="44" ht="15.15" spans="1:1">
+        <v>245</v>
+      </c>
+      <c r="B43" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A50)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="44" ht="15.15" hidden="1" spans="1:2">
       <c r="A44" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="45" ht="15.15" spans="1:1">
+        <v>293</v>
+      </c>
+      <c r="B44" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A51)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="45" ht="15.15" hidden="1" spans="1:2">
       <c r="A45" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="46" ht="15.15" spans="1:1">
+      <c r="B45" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A52)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="46" ht="15.15" hidden="1" spans="1:2">
       <c r="A46" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="47" ht="15.15" spans="1:1">
+        <v>225</v>
+      </c>
+      <c r="B46" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A53)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="47" ht="15.15" hidden="1" spans="1:2">
       <c r="A47" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="48" ht="15.15" spans="1:1">
+        <v>283</v>
+      </c>
+      <c r="B47" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A54)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="48" ht="15.15" hidden="1" spans="1:2">
       <c r="A48" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="49" ht="15.15" spans="1:1">
+        <v>101</v>
+      </c>
+      <c r="B48" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A55)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="49" ht="15.15" hidden="1" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="50" ht="15.15" spans="1:1">
+        <v>297</v>
+      </c>
+      <c r="B49" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A56)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="50" ht="15.15" hidden="1" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="51" ht="15.15" spans="1:1">
+        <v>287</v>
+      </c>
+      <c r="B50" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A57)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>postoji u Sheet1</v>
+      </c>
+    </row>
+    <row r="51" ht="15.15" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="52" ht="15.15" spans="1:1">
+        <v>289</v>
+      </c>
+      <c r="B51" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A58)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="52" ht="15.15" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="53" ht="15.15" spans="1:1">
+        <v>291</v>
+      </c>
+      <c r="B52" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A59)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="53" ht="15.15" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="54" ht="15.15" spans="1:1">
+        <v>295</v>
+      </c>
+      <c r="B53" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A60)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="54" ht="15.15" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="55" ht="15.15" spans="1:1">
+        <v>253</v>
+      </c>
+      <c r="B54" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A61)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="55" ht="15.15" spans="1:2">
       <c r="A55" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="56" ht="15.15" spans="1:1">
+        <v>191</v>
+      </c>
+      <c r="B55" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A62)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="56" ht="15.15" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="57" ht="15.15" spans="1:1">
+        <v>255</v>
+      </c>
+      <c r="B56" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A63)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="57" ht="15.15" spans="1:2">
       <c r="A57" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="58" ht="15.15" spans="1:1">
+        <v>77</v>
+      </c>
+      <c r="B57" t="str">
+        <f>IF(COUNTIF(Sheet1!$B:$AB,A64)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
+        <v>NE POSTOJI u Sheet1</v>
+      </c>
+    </row>
+    <row r="58" ht="15.15" spans="1:2">
       <c r="A58" s="2"/>
     </row>
-    <row r="59" ht="15.15" spans="1:1">
+    <row r="59" ht="15.15" spans="1:2">
       <c r="A59" s="2"/>
     </row>
-    <row r="60" ht="15.15" spans="1:1">
+    <row r="60" ht="15.15" spans="1:2">
       <c r="A60" s="2"/>
     </row>
-    <row r="61" ht="15.15" spans="1:1">
+    <row r="61" ht="15.15" spans="1:2">
       <c r="A61" s="2"/>
     </row>
-    <row r="62" ht="15.15" spans="1:1">
+    <row r="62" ht="15.15" spans="1:2">
       <c r="A62" s="2"/>
     </row>
-    <row r="63" ht="15.15" spans="1:1">
+    <row r="63" ht="15.15" spans="1:2">
       <c r="A63" s="2"/>
     </row>
-    <row r="64" ht="15.15" spans="1:1">
+    <row r="64" ht="15.15" spans="1:2">
       <c r="A64" s="2"/>
     </row>
     <row r="65" ht="15.15" spans="1:1">
@@ -9233,6 +9943,14 @@
       <c r="A877" s="2"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G57" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="equal" val="NE POSTOJI u Sheet1"/>
+      </customFilters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/testdata/configurationUAT/execute.xlsx
+++ b/testdata/configurationUAT/execute.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23160" windowHeight="9528"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$171</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="367">
   <si>
     <t>App</t>
   </si>
@@ -578,6 +578,9 @@
     <t>C70864</t>
   </si>
   <si>
+    <t>on</t>
+  </si>
+  <si>
     <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]-Internal_Urgent_Payment</t>
   </si>
   <si>
@@ -977,9 +980,6 @@
     <t>C70934</t>
   </si>
   <si>
-    <t>on</t>
-  </si>
-  <si>
     <t>Payments_Own_Account_Transfer_To_Card_[ANDROID]-From_Current_Domestic_Account</t>
   </si>
   <si>
@@ -1032,6 +1032,33 @@
   </si>
   <si>
     <t>C70943</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_List_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]-To_Current_Authorized_Account</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Details_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70948</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70949</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Statemants_Share_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70950</t>
   </si>
   <si>
     <t>Name</t>
@@ -1838,7 +1865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1887,6 +1914,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2232,7 +2260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G165"/>
+  <dimension ref="A1:G222"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="123.185185185185" customWidth="1"/>
@@ -4297,9 +4325,8 @@
       <c r="F86" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G86" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B86,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G86" s="15" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:7">
@@ -4307,10 +4334,10 @@
         <v>7</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D87" s="15" t="s">
         <v>10</v>
@@ -4331,10 +4358,10 @@
         <v>7</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>10</v>
@@ -4345,9 +4372,8 @@
       <c r="F88" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G88" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B88,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G88" s="15" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:7">
@@ -4355,10 +4381,10 @@
         <v>7</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D89" s="15" t="s">
         <v>10</v>
@@ -4379,10 +4405,10 @@
         <v>7</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>10</v>
@@ -4403,10 +4429,10 @@
         <v>7</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D91" s="15" t="s">
         <v>10</v>
@@ -4427,10 +4453,10 @@
         <v>7</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>10</v>
@@ -4451,10 +4477,10 @@
         <v>7</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D93" s="15" t="s">
         <v>10</v>
@@ -4475,10 +4501,10 @@
         <v>7</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>10</v>
@@ -4499,10 +4525,10 @@
         <v>7</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D95" s="15" t="s">
         <v>10</v>
@@ -4523,10 +4549,10 @@
         <v>7</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>10</v>
@@ -4547,10 +4573,10 @@
         <v>7</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D97" s="15" t="s">
         <v>10</v>
@@ -4571,10 +4597,10 @@
         <v>7</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>10</v>
@@ -4595,10 +4621,10 @@
         <v>7</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D99" s="15" t="s">
         <v>10</v>
@@ -4619,10 +4645,10 @@
         <v>7</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>10</v>
@@ -4643,10 +4669,10 @@
         <v>7</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D101" s="15" t="s">
         <v>10</v>
@@ -4667,10 +4693,10 @@
         <v>7</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>10</v>
@@ -4691,10 +4717,10 @@
         <v>7</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D103" s="15" t="s">
         <v>10</v>
@@ -4715,10 +4741,10 @@
         <v>7</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>10</v>
@@ -4739,10 +4765,10 @@
         <v>7</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>10</v>
@@ -4763,10 +4789,10 @@
         <v>7</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>10</v>
@@ -4787,10 +4813,10 @@
         <v>7</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D107" s="15" t="s">
         <v>10</v>
@@ -4811,10 +4837,10 @@
         <v>7</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>10</v>
@@ -4835,10 +4861,10 @@
         <v>7</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D109" s="15" t="s">
         <v>10</v>
@@ -4859,10 +4885,10 @@
         <v>7</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>10</v>
@@ -4873,9 +4899,8 @@
       <c r="F110" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G110" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B110,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G110" s="15" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:7">
@@ -4883,10 +4908,10 @@
         <v>7</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D111" s="15" t="s">
         <v>10</v>
@@ -4907,10 +4932,10 @@
         <v>7</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>10</v>
@@ -4931,10 +4956,10 @@
         <v>7</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D113" s="15" t="s">
         <v>10</v>
@@ -4955,10 +4980,10 @@
         <v>7</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>10</v>
@@ -4979,10 +5004,10 @@
         <v>7</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>10</v>
@@ -5003,10 +5028,10 @@
         <v>7</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>10</v>
@@ -5027,10 +5052,10 @@
         <v>7</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D117" s="15" t="s">
         <v>10</v>
@@ -5051,10 +5076,10 @@
         <v>7</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>10</v>
@@ -5075,10 +5100,10 @@
         <v>7</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D119" s="15" t="s">
         <v>10</v>
@@ -5099,10 +5124,10 @@
         <v>7</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>10</v>
@@ -5123,10 +5148,10 @@
         <v>7</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>10</v>
@@ -5147,10 +5172,10 @@
         <v>7</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>10</v>
@@ -5171,10 +5196,10 @@
         <v>7</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D123" s="15" t="s">
         <v>10</v>
@@ -5195,10 +5220,10 @@
         <v>7</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>10</v>
@@ -5219,10 +5244,10 @@
         <v>7</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D125" s="15" t="s">
         <v>10</v>
@@ -5243,10 +5268,10 @@
         <v>7</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>10</v>
@@ -5257,9 +5282,8 @@
       <c r="F126" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G126" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B126,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G126" s="15" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -5267,10 +5291,10 @@
         <v>7</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D127" s="15" t="s">
         <v>10</v>
@@ -5291,10 +5315,10 @@
         <v>7</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>10</v>
@@ -5315,10 +5339,10 @@
         <v>7</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D129" s="15" t="s">
         <v>10</v>
@@ -5339,10 +5363,10 @@
         <v>7</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>10</v>
@@ -5363,10 +5387,10 @@
         <v>7</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D131" s="15" t="s">
         <v>10</v>
@@ -5387,10 +5411,10 @@
         <v>7</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>10</v>
@@ -5411,10 +5435,10 @@
         <v>7</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>10</v>
@@ -5435,10 +5459,10 @@
         <v>7</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>10</v>
@@ -5459,10 +5483,10 @@
         <v>7</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D135" s="15" t="s">
         <v>10</v>
@@ -5483,10 +5507,10 @@
         <v>7</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>10</v>
@@ -5507,10 +5531,10 @@
         <v>7</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D137" s="15" t="s">
         <v>10</v>
@@ -5531,10 +5555,10 @@
         <v>7</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>10</v>
@@ -5555,10 +5579,10 @@
         <v>7</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D139" s="15" t="s">
         <v>10</v>
@@ -5579,10 +5603,10 @@
         <v>7</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>10</v>
@@ -5603,10 +5627,10 @@
         <v>7</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D141" s="15" t="s">
         <v>10</v>
@@ -5627,10 +5651,10 @@
         <v>7</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>10</v>
@@ -5651,10 +5675,10 @@
         <v>7</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>10</v>
@@ -5675,10 +5699,10 @@
         <v>7</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>10</v>
@@ -5699,10 +5723,10 @@
         <v>7</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D145" s="15" t="s">
         <v>10</v>
@@ -5723,10 +5747,10 @@
         <v>7</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>10</v>
@@ -5747,10 +5771,10 @@
         <v>7</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D147" s="15" t="s">
         <v>10</v>
@@ -5771,10 +5795,10 @@
         <v>7</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>10</v>
@@ -5795,10 +5819,10 @@
         <v>7</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D149" s="15" t="s">
         <v>10</v>
@@ -5819,10 +5843,10 @@
         <v>7</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>10</v>
@@ -5843,10 +5867,10 @@
         <v>7</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D151" s="15" t="s">
         <v>10</v>
@@ -5867,10 +5891,10 @@
         <v>7</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>10</v>
@@ -5891,10 +5915,10 @@
         <v>7</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D153" s="15" t="s">
         <v>10</v>
@@ -5915,10 +5939,10 @@
         <v>7</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D154" s="15" t="s">
         <v>10</v>
@@ -5942,7 +5966,7 @@
         <v>77</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>10</v>
@@ -5959,12 +5983,14 @@
       </c>
     </row>
     <row r="156" customFormat="1" spans="1:7">
-      <c r="A156" s="15"/>
+      <c r="A156" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B156" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>10</v>
@@ -5976,11 +6002,13 @@
         <v>12</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="157" customFormat="1" spans="1:7">
-      <c r="A157" s="15"/>
+      <c r="A157" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B157" s="15" t="s">
         <v>315</v>
       </c>
@@ -5997,11 +6025,13 @@
         <v>12</v>
       </c>
       <c r="G157" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="158" customFormat="1" spans="1:7">
-      <c r="A158" s="15"/>
+      <c r="A158" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B158" s="15" t="s">
         <v>317</v>
       </c>
@@ -6018,11 +6048,13 @@
         <v>12</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="159" customFormat="1" spans="1:7">
-      <c r="A159" s="15"/>
+      <c r="A159" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B159" s="15" t="s">
         <v>319</v>
       </c>
@@ -6039,11 +6071,13 @@
         <v>12</v>
       </c>
       <c r="G159" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="160" customFormat="1" spans="1:7">
-      <c r="A160" s="15"/>
+      <c r="A160" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B160" s="15" t="s">
         <v>321</v>
       </c>
@@ -6060,11 +6094,13 @@
         <v>12</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="161" customFormat="1" spans="1:7">
-      <c r="A161" s="15"/>
+      <c r="A161" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B161" s="15" t="s">
         <v>323</v>
       </c>
@@ -6081,11 +6117,13 @@
         <v>12</v>
       </c>
       <c r="G161" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="162" customFormat="1" spans="1:7">
-      <c r="A162" s="15"/>
+      <c r="A162" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B162" s="15" t="s">
         <v>325</v>
       </c>
@@ -6102,10 +6140,13 @@
         <v>12</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:7">
+      <c r="A163" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B163" s="15" t="s">
         <v>327</v>
       </c>
@@ -6122,10 +6163,13 @@
         <v>12</v>
       </c>
       <c r="G163" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="164" spans="1:7">
+      <c r="A164" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B164" s="15" t="s">
         <v>329</v>
       </c>
@@ -6142,10 +6186,13 @@
         <v>12</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>314</v>
+        <v>181</v>
       </c>
     </row>
     <row r="165" spans="1:7">
+      <c r="A165" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="B165" s="15" t="s">
         <v>331</v>
       </c>
@@ -6162,11 +6209,622 @@
         <v>12</v>
       </c>
       <c r="G165" s="15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" spans="1:7">
+      <c r="A166" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B166" s="15" t="s">
+        <v>333</v>
+      </c>
+      <c r="C166" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="D166" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E166" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="167" customFormat="1" spans="1:7">
+      <c r="A167" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B167" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="C167" s="15" t="s">
         <v>314</v>
       </c>
+      <c r="D167" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E167" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G167" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="168" customFormat="1" spans="1:7">
+      <c r="A168" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B168" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="C168" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="D168" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E168" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G168" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="169" customFormat="1" spans="1:7">
+      <c r="A169" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="C169" s="15" t="s">
+        <v>318</v>
+      </c>
+      <c r="D169" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E169" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G169" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="170" customFormat="1" spans="1:7">
+      <c r="A170" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="C170" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="D170" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E170" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="171" customFormat="1" spans="1:7">
+      <c r="A171" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="C171" s="15" t="s">
+        <v>339</v>
+      </c>
+      <c r="D171" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E171" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G171" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="172" customFormat="1" spans="1:7">
+      <c r="A172" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="C172" s="15" t="s">
+        <v>341</v>
+      </c>
+      <c r="D172" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E172" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G172" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173" customFormat="1" spans="1:7">
+      <c r="A173" s="15"/>
+      <c r="B173" s="15"/>
+      <c r="C173" s="15"/>
+      <c r="D173" s="15"/>
+      <c r="E173" s="15"/>
+      <c r="F173" s="17"/>
+      <c r="G173" s="15"/>
+    </row>
+    <row r="174" customFormat="1" spans="1:7">
+      <c r="A174" s="15"/>
+      <c r="B174" s="15"/>
+      <c r="C174" s="15"/>
+      <c r="D174" s="15"/>
+      <c r="E174" s="15"/>
+      <c r="F174" s="17"/>
+      <c r="G174" s="15"/>
+    </row>
+    <row r="175" customFormat="1" spans="1:7">
+      <c r="A175" s="15"/>
+      <c r="B175" s="15"/>
+      <c r="C175" s="15"/>
+      <c r="D175" s="15"/>
+      <c r="E175" s="15"/>
+      <c r="F175" s="17"/>
+      <c r="G175" s="15"/>
+    </row>
+    <row r="176" customFormat="1" spans="1:7">
+      <c r="A176" s="15"/>
+      <c r="B176" s="15"/>
+      <c r="C176" s="15"/>
+      <c r="D176" s="15"/>
+      <c r="E176" s="15"/>
+      <c r="F176" s="17"/>
+      <c r="G176" s="15"/>
+    </row>
+    <row r="177" customFormat="1" spans="1:7">
+      <c r="A177" s="15"/>
+      <c r="B177" s="15"/>
+      <c r="C177" s="15"/>
+      <c r="D177" s="15"/>
+      <c r="E177" s="15"/>
+      <c r="F177" s="17"/>
+      <c r="G177" s="15"/>
+    </row>
+    <row r="178" customFormat="1" spans="1:7">
+      <c r="A178" s="15"/>
+      <c r="B178" s="15"/>
+      <c r="C178" s="15"/>
+      <c r="D178" s="15"/>
+      <c r="E178" s="15"/>
+      <c r="F178" s="17"/>
+      <c r="G178" s="15"/>
+    </row>
+    <row r="179" customFormat="1" spans="1:7">
+      <c r="A179" s="15"/>
+      <c r="B179" s="15"/>
+      <c r="C179" s="15"/>
+      <c r="D179" s="15"/>
+      <c r="E179" s="15"/>
+      <c r="F179" s="17"/>
+      <c r="G179" s="15"/>
+    </row>
+    <row r="180" customFormat="1" spans="1:7">
+      <c r="A180" s="15"/>
+      <c r="B180" s="15"/>
+      <c r="C180" s="15"/>
+      <c r="D180" s="15"/>
+      <c r="E180" s="15"/>
+      <c r="F180" s="17"/>
+      <c r="G180" s="15"/>
+    </row>
+    <row r="181" customFormat="1" spans="1:7">
+      <c r="A181" s="15"/>
+      <c r="B181" s="15"/>
+      <c r="C181" s="15"/>
+      <c r="D181" s="15"/>
+      <c r="E181" s="15"/>
+      <c r="F181" s="17"/>
+      <c r="G181" s="15"/>
+    </row>
+    <row r="182" customFormat="1" spans="1:7">
+      <c r="A182" s="15"/>
+      <c r="B182" s="15"/>
+      <c r="C182" s="15"/>
+      <c r="D182" s="15"/>
+      <c r="E182" s="15"/>
+      <c r="F182" s="17"/>
+      <c r="G182" s="15"/>
+    </row>
+    <row r="183" customFormat="1" spans="1:7">
+      <c r="A183" s="15"/>
+      <c r="B183" s="15"/>
+      <c r="C183" s="15"/>
+      <c r="D183" s="15"/>
+      <c r="E183" s="15"/>
+      <c r="F183" s="17"/>
+      <c r="G183" s="15"/>
+    </row>
+    <row r="184" customFormat="1" spans="1:7">
+      <c r="A184" s="15"/>
+      <c r="B184" s="15"/>
+      <c r="C184" s="15"/>
+      <c r="D184" s="15"/>
+      <c r="E184" s="15"/>
+      <c r="F184" s="17"/>
+      <c r="G184" s="15"/>
+    </row>
+    <row r="185" customFormat="1" spans="1:7">
+      <c r="A185" s="15"/>
+      <c r="B185" s="15"/>
+      <c r="C185" s="15"/>
+      <c r="D185" s="15"/>
+      <c r="E185" s="15"/>
+      <c r="F185" s="17"/>
+      <c r="G185" s="15"/>
+    </row>
+    <row r="186" customFormat="1" spans="1:7">
+      <c r="A186" s="15"/>
+      <c r="B186" s="15"/>
+      <c r="C186" s="15"/>
+      <c r="D186" s="15"/>
+      <c r="E186" s="15"/>
+      <c r="F186" s="17"/>
+      <c r="G186" s="15"/>
+    </row>
+    <row r="187" customFormat="1" spans="1:7">
+      <c r="A187" s="15"/>
+      <c r="B187" s="15"/>
+      <c r="C187" s="15"/>
+      <c r="D187" s="15"/>
+      <c r="E187" s="15"/>
+      <c r="F187" s="17"/>
+      <c r="G187" s="15"/>
+    </row>
+    <row r="188" customFormat="1" spans="1:7">
+      <c r="A188" s="15"/>
+      <c r="B188" s="15"/>
+      <c r="C188" s="15"/>
+      <c r="D188" s="15"/>
+      <c r="E188" s="15"/>
+      <c r="F188" s="17"/>
+      <c r="G188" s="15"/>
+    </row>
+    <row r="189" customFormat="1" spans="1:7">
+      <c r="A189" s="15"/>
+      <c r="B189" s="15"/>
+      <c r="C189" s="15"/>
+      <c r="D189" s="15"/>
+      <c r="E189" s="15"/>
+      <c r="F189" s="17"/>
+      <c r="G189" s="15"/>
+    </row>
+    <row r="190" customFormat="1" spans="1:7">
+      <c r="A190" s="15"/>
+      <c r="B190" s="15"/>
+      <c r="C190" s="15"/>
+      <c r="D190" s="15"/>
+      <c r="E190" s="15"/>
+      <c r="F190" s="17"/>
+      <c r="G190" s="15"/>
+    </row>
+    <row r="191" customFormat="1" spans="1:7">
+      <c r="A191" s="15"/>
+      <c r="B191" s="15"/>
+      <c r="C191" s="15"/>
+      <c r="D191" s="15"/>
+      <c r="E191" s="15"/>
+      <c r="F191" s="17"/>
+      <c r="G191" s="15"/>
+    </row>
+    <row r="192" customFormat="1" spans="1:7">
+      <c r="A192" s="15"/>
+      <c r="B192" s="15"/>
+      <c r="C192" s="15"/>
+      <c r="D192" s="15"/>
+      <c r="E192" s="15"/>
+      <c r="F192" s="17"/>
+      <c r="G192" s="15"/>
+    </row>
+    <row r="193" customFormat="1" spans="1:7">
+      <c r="A193" s="15"/>
+      <c r="B193" s="15"/>
+      <c r="C193" s="15"/>
+      <c r="D193" s="15"/>
+      <c r="E193" s="15"/>
+      <c r="F193" s="17"/>
+      <c r="G193" s="15"/>
+    </row>
+    <row r="194" customFormat="1" spans="1:7">
+      <c r="A194" s="15"/>
+      <c r="B194" s="15"/>
+      <c r="C194" s="15"/>
+      <c r="D194" s="15"/>
+      <c r="E194" s="15"/>
+      <c r="F194" s="17"/>
+      <c r="G194" s="15"/>
+    </row>
+    <row r="195" customFormat="1" spans="1:7">
+      <c r="A195" s="15"/>
+      <c r="B195" s="15"/>
+      <c r="C195" s="15"/>
+      <c r="D195" s="15"/>
+      <c r="E195" s="15"/>
+      <c r="F195" s="17"/>
+      <c r="G195" s="15"/>
+    </row>
+    <row r="196" customFormat="1" spans="1:7">
+      <c r="A196" s="15"/>
+      <c r="B196" s="15"/>
+      <c r="C196" s="15"/>
+      <c r="D196" s="15"/>
+      <c r="E196" s="15"/>
+      <c r="F196" s="17"/>
+      <c r="G196" s="15"/>
+    </row>
+    <row r="197" customFormat="1" spans="1:7">
+      <c r="A197" s="15"/>
+      <c r="B197" s="15"/>
+      <c r="C197" s="15"/>
+      <c r="D197" s="15"/>
+      <c r="E197" s="15"/>
+      <c r="F197" s="17"/>
+      <c r="G197" s="15"/>
+    </row>
+    <row r="198" customFormat="1" spans="1:7">
+      <c r="A198" s="15"/>
+      <c r="B198" s="15"/>
+      <c r="C198" s="15"/>
+      <c r="D198" s="15"/>
+      <c r="E198" s="15"/>
+      <c r="F198" s="17"/>
+      <c r="G198" s="15"/>
+    </row>
+    <row r="199" customFormat="1" spans="1:7">
+      <c r="A199" s="15"/>
+      <c r="B199" s="15"/>
+      <c r="C199" s="15"/>
+      <c r="D199" s="15"/>
+      <c r="E199" s="15"/>
+      <c r="F199" s="17"/>
+      <c r="G199" s="15"/>
+    </row>
+    <row r="200" customFormat="1" spans="1:7">
+      <c r="A200" s="15"/>
+      <c r="B200" s="15"/>
+      <c r="C200" s="15"/>
+      <c r="D200" s="15"/>
+      <c r="E200" s="15"/>
+      <c r="F200" s="17"/>
+      <c r="G200" s="15"/>
+    </row>
+    <row r="201" customFormat="1" spans="1:7">
+      <c r="A201" s="15"/>
+      <c r="B201" s="15"/>
+      <c r="C201" s="15"/>
+      <c r="D201" s="15"/>
+      <c r="E201" s="15"/>
+      <c r="F201" s="17"/>
+      <c r="G201" s="15"/>
+    </row>
+    <row r="202" customFormat="1" spans="1:7">
+      <c r="A202" s="15"/>
+      <c r="B202" s="15"/>
+      <c r="C202" s="15"/>
+      <c r="D202" s="15"/>
+      <c r="E202" s="15"/>
+      <c r="F202" s="17"/>
+      <c r="G202" s="15"/>
+    </row>
+    <row r="203" customFormat="1" spans="1:7">
+      <c r="A203" s="15"/>
+      <c r="B203" s="15"/>
+      <c r="C203" s="15"/>
+      <c r="D203" s="15"/>
+      <c r="E203" s="15"/>
+      <c r="F203" s="17"/>
+      <c r="G203" s="15"/>
+    </row>
+    <row r="204" customFormat="1" spans="1:7">
+      <c r="A204" s="15"/>
+      <c r="B204" s="15"/>
+      <c r="C204" s="15"/>
+      <c r="D204" s="15"/>
+      <c r="E204" s="15"/>
+      <c r="F204" s="17"/>
+      <c r="G204" s="15"/>
+    </row>
+    <row r="205" customFormat="1" spans="1:7">
+      <c r="A205" s="15"/>
+      <c r="B205" s="15"/>
+      <c r="C205" s="15"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="15"/>
+      <c r="F205" s="17"/>
+      <c r="G205" s="15"/>
+    </row>
+    <row r="206" customFormat="1" spans="1:7">
+      <c r="A206" s="15"/>
+      <c r="B206" s="15"/>
+      <c r="C206" s="15"/>
+      <c r="D206" s="15"/>
+      <c r="E206" s="15"/>
+      <c r="F206" s="17"/>
+      <c r="G206" s="15"/>
+    </row>
+    <row r="207" customFormat="1" spans="1:7">
+      <c r="A207" s="15"/>
+      <c r="B207" s="15"/>
+      <c r="C207" s="15"/>
+      <c r="D207" s="15"/>
+      <c r="E207" s="15"/>
+      <c r="F207" s="17"/>
+      <c r="G207" s="15"/>
+    </row>
+    <row r="208" customFormat="1" spans="1:7">
+      <c r="A208" s="15"/>
+      <c r="B208" s="15"/>
+      <c r="C208" s="15"/>
+      <c r="D208" s="15"/>
+      <c r="E208" s="15"/>
+      <c r="F208" s="17"/>
+      <c r="G208" s="15"/>
+    </row>
+    <row r="209" customFormat="1" spans="1:7">
+      <c r="A209" s="15"/>
+      <c r="B209" s="15"/>
+      <c r="C209" s="15"/>
+      <c r="D209" s="15"/>
+      <c r="E209" s="15"/>
+      <c r="F209" s="17"/>
+      <c r="G209" s="15"/>
+    </row>
+    <row r="210" customFormat="1" spans="1:7">
+      <c r="A210" s="15"/>
+      <c r="B210" s="15"/>
+      <c r="C210" s="15"/>
+      <c r="D210" s="15"/>
+      <c r="E210" s="15"/>
+      <c r="F210" s="17"/>
+      <c r="G210" s="15"/>
+    </row>
+    <row r="211" customFormat="1" spans="1:7">
+      <c r="A211" s="15"/>
+      <c r="B211" s="15"/>
+      <c r="C211" s="15"/>
+      <c r="D211" s="15"/>
+      <c r="E211" s="15"/>
+      <c r="F211" s="17"/>
+      <c r="G211" s="15"/>
+    </row>
+    <row r="212" customFormat="1" spans="1:7">
+      <c r="A212" s="15"/>
+      <c r="B212" s="15"/>
+      <c r="C212" s="15"/>
+      <c r="D212" s="15"/>
+      <c r="E212" s="15"/>
+      <c r="F212" s="17"/>
+      <c r="G212" s="15"/>
+    </row>
+    <row r="213" customFormat="1" spans="1:7">
+      <c r="A213" s="15"/>
+      <c r="B213" s="15"/>
+      <c r="C213" s="15"/>
+      <c r="D213" s="15"/>
+      <c r="E213" s="15"/>
+      <c r="F213" s="17"/>
+      <c r="G213" s="15"/>
+    </row>
+    <row r="214" customFormat="1" spans="1:7">
+      <c r="A214" s="15"/>
+      <c r="B214" s="15"/>
+      <c r="C214" s="15"/>
+      <c r="D214" s="15"/>
+      <c r="E214" s="15"/>
+      <c r="F214" s="17"/>
+      <c r="G214" s="15"/>
+    </row>
+    <row r="215" customFormat="1" spans="1:7">
+      <c r="A215" s="15"/>
+      <c r="B215" s="15"/>
+      <c r="C215" s="15"/>
+      <c r="D215" s="15"/>
+      <c r="E215" s="15"/>
+      <c r="F215" s="17"/>
+      <c r="G215" s="15"/>
+    </row>
+    <row r="216" customFormat="1" spans="1:7">
+      <c r="A216" s="15"/>
+      <c r="B216" s="15"/>
+      <c r="C216" s="15"/>
+      <c r="D216" s="15"/>
+      <c r="E216" s="15"/>
+      <c r="F216" s="17"/>
+      <c r="G216" s="15"/>
+    </row>
+    <row r="217" customFormat="1" spans="1:7">
+      <c r="A217" s="15"/>
+      <c r="B217" s="15"/>
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="17"/>
+      <c r="G217" s="15"/>
+    </row>
+    <row r="218" customFormat="1" spans="1:7">
+      <c r="A218" s="15"/>
+      <c r="B218" s="15"/>
+      <c r="C218" s="15"/>
+      <c r="D218" s="15"/>
+      <c r="E218" s="15"/>
+      <c r="F218" s="17"/>
+      <c r="G218" s="15"/>
+    </row>
+    <row r="219" customFormat="1" spans="1:7">
+      <c r="A219" s="15"/>
+      <c r="B219" s="15"/>
+      <c r="C219" s="15"/>
+      <c r="D219" s="15"/>
+      <c r="E219" s="15"/>
+      <c r="F219" s="17"/>
+      <c r="G219" s="15"/>
+    </row>
+    <row r="220" customFormat="1" spans="1:7">
+      <c r="A220" s="15"/>
+      <c r="B220" s="15"/>
+      <c r="C220" s="15"/>
+      <c r="D220" s="15"/>
+      <c r="E220" s="15"/>
+      <c r="F220" s="17"/>
+      <c r="G220" s="15"/>
+    </row>
+    <row r="221" customFormat="1" spans="1:7">
+      <c r="A221" s="15"/>
+      <c r="B221" s="15"/>
+      <c r="C221" s="15"/>
+      <c r="D221" s="15"/>
+      <c r="E221" s="15"/>
+      <c r="F221" s="17"/>
+      <c r="G221" s="15"/>
+    </row>
+    <row r="222" customFormat="1" spans="1:7">
+      <c r="A222" s="15"/>
+      <c r="B222" s="15"/>
+      <c r="C222" s="15"/>
+      <c r="D222" s="15"/>
+      <c r="E222" s="15"/>
+      <c r="F222" s="17"/>
+      <c r="G222" s="15"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G164" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G171" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B128">
@@ -6267,19 +6925,19 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" spans="1:5">
@@ -6287,21 +6945,21 @@
         <v>177</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" spans="1:5">
@@ -6309,60 +6967,60 @@
         <v>167</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" ht="77" customHeight="1" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:5">
@@ -6370,32 +7028,32 @@
         <v>15</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:5">
@@ -6403,10 +7061,10 @@
         <v>87</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:5">
@@ -6414,10 +7072,10 @@
         <v>163</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:5">
@@ -6425,10 +7083,10 @@
         <v>179</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:5">
@@ -6436,95 +7094,95 @@
         <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:5">
@@ -6532,10 +7190,10 @@
         <v>89</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:5">
@@ -6543,10 +7201,10 @@
         <v>65</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:5">
@@ -6554,10 +7212,10 @@
         <v>37</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -6567,10 +7225,10 @@
         <v>8</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:5">
@@ -6578,10 +7236,10 @@
         <v>71</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:5">
@@ -6589,10 +7247,10 @@
         <v>57</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" spans="1:5">
@@ -6600,47 +7258,47 @@
         <v>85</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" s="3" customFormat="1" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>347</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="31" s="3" customFormat="1" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>347</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>338</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>347</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>338</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
@@ -6650,10 +7308,10 @@
         <v>131</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:5">
@@ -6661,24 +7319,24 @@
         <v>115</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="115.2" spans="1:5">
       <c r="A35" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>340</v>
-      </c>
       <c r="E35" s="7" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:5">
@@ -6686,10 +7344,10 @@
         <v>79</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:5">
@@ -6697,21 +7355,21 @@
         <v>159</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:5">
@@ -6719,10 +7377,10 @@
         <v>169</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:5">
@@ -6730,10 +7388,10 @@
         <v>111</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:5">
@@ -6741,10 +7399,10 @@
         <v>133</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:5">
@@ -6752,10 +7410,10 @@
         <v>95</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:5">
@@ -6763,10 +7421,10 @@
         <v>123</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:5">
@@ -6774,10 +7432,10 @@
         <v>173</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:5">
@@ -6785,73 +7443,73 @@
         <v>175</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="28.8" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:5">
       <c r="A49" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:5">
@@ -6859,21 +7517,21 @@
         <v>41</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="100.8" spans="1:5">
@@ -6881,69 +7539,69 @@
         <v>17</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:5">
       <c r="A60" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:5">
       <c r="A61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:5">
       <c r="A62" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="63" s="3" customFormat="1" spans="1:5">
       <c r="A63" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:5">
       <c r="A64" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -6968,7 +7626,7 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" ht="15.15" hidden="1" spans="1:7">
@@ -6980,7 +7638,7 @@
         <v>postoji u Sheet1</v>
       </c>
       <c r="F2" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="G2" t="str">
         <f>IF(ISNUMBER(MATCH(B2,Sheet3!$A:$A,0)),"on","off")</f>
@@ -6989,7 +7647,7 @@
     </row>
     <row r="3" ht="15.15" hidden="1" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B3" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A10)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -6998,7 +7656,7 @@
     </row>
     <row r="4" ht="15.15" hidden="1" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B4" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A11)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7034,7 +7692,7 @@
     </row>
     <row r="8" ht="15.15" hidden="1" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B8" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A15)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7070,7 +7728,7 @@
     </row>
     <row r="12" ht="15.15" hidden="1" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B12" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A19)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7079,7 +7737,7 @@
     </row>
     <row r="13" ht="15.15" hidden="1" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B13" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A20)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7097,7 +7755,7 @@
     </row>
     <row r="15" ht="15.15" hidden="1" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B15" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A22)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7106,7 +7764,7 @@
     </row>
     <row r="16" ht="15.15" hidden="1" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B16" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A23)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7115,7 +7773,7 @@
     </row>
     <row r="17" ht="15.15" hidden="1" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B17" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A24)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7133,7 +7791,7 @@
     </row>
     <row r="19" ht="15.15" hidden="1" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B19" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A26)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7142,7 +7800,7 @@
     </row>
     <row r="20" ht="15.15" hidden="1" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B20" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A27)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7160,7 +7818,7 @@
     </row>
     <row r="22" ht="15.15" hidden="1" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B22" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A29)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7169,7 +7827,7 @@
     </row>
     <row r="23" ht="15.15" hidden="1" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B23" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A30)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7178,7 +7836,7 @@
     </row>
     <row r="24" ht="15.15" hidden="1" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B24" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A31)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7187,7 +7845,7 @@
     </row>
     <row r="25" ht="15.15" hidden="1" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A32)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7196,7 +7854,7 @@
     </row>
     <row r="26" ht="15.15" hidden="1" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B26" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A33)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7205,7 +7863,7 @@
     </row>
     <row r="27" ht="15.15" hidden="1" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B27" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A34)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7214,7 +7872,7 @@
     </row>
     <row r="28" ht="15.15" hidden="1" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B28" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A35)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7232,7 +7890,7 @@
     </row>
     <row r="30" ht="15.15" hidden="1" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A37)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7241,7 +7899,7 @@
     </row>
     <row r="31" ht="15.15" hidden="1" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B31" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A38)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7250,7 +7908,7 @@
     </row>
     <row r="32" ht="15.15" hidden="1" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B32" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A39)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7259,7 +7917,7 @@
     </row>
     <row r="33" ht="15.15" hidden="1" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B33" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A40)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7268,7 +7926,7 @@
     </row>
     <row r="34" ht="15.15" hidden="1" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B34" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A41)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7277,7 +7935,7 @@
     </row>
     <row r="35" ht="15.15" hidden="1" spans="1:2">
       <c r="A35" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B35" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A42)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7286,7 +7944,7 @@
     </row>
     <row r="36" ht="15.15" hidden="1" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B36" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A43)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7295,7 +7953,7 @@
     </row>
     <row r="37" ht="15.15" hidden="1" spans="1:2">
       <c r="A37" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B37" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A44)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7304,7 +7962,7 @@
     </row>
     <row r="38" ht="15.15" hidden="1" spans="1:2">
       <c r="A38" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B38" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A45)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7313,7 +7971,7 @@
     </row>
     <row r="39" ht="15.15" hidden="1" spans="1:2">
       <c r="A39" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B39" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A46)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7322,7 +7980,7 @@
     </row>
     <row r="40" ht="15.15" hidden="1" spans="1:2">
       <c r="A40" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B40" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A47)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7331,7 +7989,7 @@
     </row>
     <row r="41" ht="15.15" hidden="1" spans="1:2">
       <c r="A41" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B41" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A48)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7340,7 +7998,7 @@
     </row>
     <row r="42" ht="15.15" hidden="1" spans="1:2">
       <c r="A42" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B42" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A49)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7349,7 +8007,7 @@
     </row>
     <row r="43" ht="15.15" hidden="1" spans="1:2">
       <c r="A43" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B43" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A50)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7358,7 +8016,7 @@
     </row>
     <row r="44" ht="15.15" hidden="1" spans="1:2">
       <c r="A44" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B44" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A51)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7376,7 +8034,7 @@
     </row>
     <row r="46" ht="15.15" hidden="1" spans="1:2">
       <c r="A46" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B46" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A53)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7385,7 +8043,7 @@
     </row>
     <row r="47" ht="15.15" hidden="1" spans="1:2">
       <c r="A47" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B47" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A54)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7403,7 +8061,7 @@
     </row>
     <row r="49" ht="15.15" hidden="1" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A56)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7412,7 +8070,7 @@
     </row>
     <row r="50" ht="15.15" hidden="1" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B50" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A57)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7421,7 +8079,7 @@
     </row>
     <row r="51" ht="15.15" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B51" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A58)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7430,7 +8088,7 @@
     </row>
     <row r="52" ht="15.15" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B52" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A59)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7439,7 +8097,7 @@
     </row>
     <row r="53" ht="15.15" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B53" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A60)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7448,7 +8106,7 @@
     </row>
     <row r="54" ht="15.15" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B54" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A61)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7457,7 +8115,7 @@
     </row>
     <row r="55" ht="15.15" spans="1:2">
       <c r="A55" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A62)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7466,7 +8124,7 @@
     </row>
     <row r="56" ht="15.15" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B56" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A63)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>

--- a/testdata/configurationUAT/execute.xlsx
+++ b/testdata/configurationUAT/execute.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23160" windowHeight="9528"/>
+    <workbookView windowWidth="22512" windowHeight="9528"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet3!$A$1:$G$57</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="400">
   <si>
     <t>App</t>
   </si>
@@ -74,6 +74,9 @@
     <t>data</t>
   </si>
   <si>
+    <t>on</t>
+  </si>
+  <si>
     <t>Product_Summary-Loan_List_[MOB_ANDROID]</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
     <t>C70782</t>
   </si>
   <si>
+    <t>off</t>
+  </si>
+  <si>
     <t>Product_Summary-Edit_Product_view-edit_name_of_account-invalid_[MOB_ANDROID]_6</t>
   </si>
   <si>
@@ -578,9 +584,6 @@
     <t>C70864</t>
   </si>
   <si>
-    <t>on</t>
-  </si>
-  <si>
     <t>Payments-Domestic_Payments-Confirmation_[MOB_ANDROID]-Internal_Urgent_Payment</t>
   </si>
   <si>
@@ -1034,15 +1037,27 @@
     <t>C70943</t>
   </si>
   <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]-To_Current_Authorized_Account</t>
+  </si>
+  <si>
+    <t>C70944</t>
+  </si>
+  <si>
     <t>Credit_Cards_Transactions_List_[MOB_ANDROID]</t>
   </si>
   <si>
-    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[MOB_ANDROID]-To_Current_Authorized_Account</t>
+    <t>C70945</t>
   </si>
   <si>
     <t>Credit_Cards_Transactions_Details_[MOB_ANDROID]</t>
   </si>
   <si>
+    <t>C70946</t>
+  </si>
+  <si>
+    <t>C70947</t>
+  </si>
+  <si>
     <t>Current_Accounts_RSD_Statemants_Share_[MOB_ANDROID]</t>
   </si>
   <si>
@@ -1059,6 +1074,90 @@
   </si>
   <si>
     <t>C70950</t>
+  </si>
+  <si>
+    <t>Authentication_Mobile_Login_Forgot_PIN_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70951</t>
+  </si>
+  <si>
+    <t>Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70952</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70953</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Filter_By_Type_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70954</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Amount_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70955</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70956</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_Multiple_Filter_Invalid_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70957</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Search_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70958</t>
+  </si>
+  <si>
+    <t>Credit_Cards_Transactions_Filter_By_Date_Predefined_Date_Range_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70959</t>
+  </si>
+  <si>
+    <t>Loan_Accounts_Header_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70960</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_Input_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70961</t>
+  </si>
+  <si>
+    <t>Manage_Products_Favorite_account_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70962</t>
+  </si>
+  <si>
+    <t>Manage_Products_Favorite_account_[MOB_ANDROID]-Removal_Of_The_Favorite_Account</t>
+  </si>
+  <si>
+    <t>C70963</t>
+  </si>
+  <si>
+    <t>Credit_Cards-Transactions-Filter-Filter_By_Status_[MOB_ANDROID]</t>
+  </si>
+  <si>
+    <t>C70964</t>
   </si>
   <si>
     <t>Name</t>
@@ -1559,7 +1658,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1617,6 +1716,43 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1741,7 +1877,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1753,34 +1889,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1865,7 +2001,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
@@ -1914,7 +2050,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2260,10 +2405,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="123.185185185185" customWidth="1"/>
+    <col min="2" max="2" width="112.574074074074" customWidth="1"/>
     <col min="4" max="5" width="10.4259259259259" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2309,9 +2454,8 @@
       <c r="F2" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B2,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G2" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="1" spans="1:7">
@@ -2319,10 +2463,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>10</v>
@@ -2333,9 +2477,8 @@
       <c r="F3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B3,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G3" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="1" spans="1:7">
@@ -2343,10 +2486,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>10</v>
@@ -2357,9 +2500,8 @@
       <c r="F4" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B4,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G4" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="1" spans="1:7">
@@ -2367,10 +2509,10 @@
         <v>7</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>10</v>
@@ -2381,9 +2523,8 @@
       <c r="F5" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B5,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G5" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -2391,23 +2532,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="15" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B6,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -2415,10 +2555,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>10</v>
@@ -2429,9 +2569,8 @@
       <c r="F7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B7,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G7" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -2439,10 +2578,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>10</v>
@@ -2453,9 +2592,8 @@
       <c r="F8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B8,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G8" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:7">
@@ -2463,10 +2601,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>10</v>
@@ -2477,9 +2615,8 @@
       <c r="F9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B9,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G9" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10" customFormat="1" spans="1:7">
@@ -2487,10 +2624,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>10</v>
@@ -2501,9 +2638,8 @@
       <c r="F10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B10,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G10" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:7">
@@ -2511,10 +2647,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>10</v>
@@ -2525,9 +2661,8 @@
       <c r="F11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B11,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G11" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:7">
@@ -2535,10 +2670,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>10</v>
@@ -2549,9 +2684,8 @@
       <c r="F12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B12,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G12" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:7">
@@ -2559,10 +2693,10 @@
         <v>7</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>10</v>
@@ -2573,9 +2707,8 @@
       <c r="F13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B13,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G13" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:7">
@@ -2583,10 +2716,10 @@
         <v>7</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>10</v>
@@ -2597,9 +2730,8 @@
       <c r="F14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B14,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G14" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:7">
@@ -2607,10 +2739,10 @@
         <v>7</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>10</v>
@@ -2621,9 +2753,8 @@
       <c r="F15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B15,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G15" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:7">
@@ -2631,10 +2762,10 @@
         <v>7</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>10</v>
@@ -2645,9 +2776,8 @@
       <c r="F16" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B16,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G16" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17" customFormat="1" spans="1:7">
@@ -2655,10 +2785,10 @@
         <v>7</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>10</v>
@@ -2669,9 +2799,8 @@
       <c r="F17" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G17" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B17,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G17" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="1" spans="1:7">
@@ -2679,10 +2808,10 @@
         <v>7</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>10</v>
@@ -2693,9 +2822,8 @@
       <c r="F18" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G18" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B18,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G18" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="19" customFormat="1" spans="1:7">
@@ -2703,10 +2831,10 @@
         <v>7</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>10</v>
@@ -2717,9 +2845,8 @@
       <c r="F19" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B19,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G19" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20" customFormat="1" spans="1:7">
@@ -2727,10 +2854,10 @@
         <v>7</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>10</v>
@@ -2741,9 +2868,8 @@
       <c r="F20" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B20,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G20" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:7">
@@ -2751,10 +2877,10 @@
         <v>7</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>10</v>
@@ -2765,9 +2891,8 @@
       <c r="F21" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B21,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G21" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:7">
@@ -2775,10 +2900,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>10</v>
@@ -2789,9 +2914,8 @@
       <c r="F22" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B22,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G22" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23" customFormat="1" spans="1:7">
@@ -2799,10 +2923,10 @@
         <v>7</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>10</v>
@@ -2813,9 +2937,8 @@
       <c r="F23" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B23,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G23" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24" customFormat="1" spans="1:7">
@@ -2823,10 +2946,10 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>10</v>
@@ -2837,9 +2960,8 @@
       <c r="F24" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B24,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G24" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:7">
@@ -2847,10 +2969,10 @@
         <v>7</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D25" s="15" t="s">
         <v>10</v>
@@ -2861,9 +2983,8 @@
       <c r="F25" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B25,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G25" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26" customFormat="1" spans="1:7">
@@ -2871,10 +2992,10 @@
         <v>7</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>10</v>
@@ -2885,9 +3006,8 @@
       <c r="F26" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B26,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G26" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:7">
@@ -2895,10 +3015,10 @@
         <v>7</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D27" s="15" t="s">
         <v>10</v>
@@ -2909,9 +3029,8 @@
       <c r="F27" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B27,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G27" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="1" spans="1:7">
@@ -2919,10 +3038,10 @@
         <v>7</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>10</v>
@@ -2933,9 +3052,8 @@
       <c r="F28" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B28,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G28" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="29" customFormat="1" spans="1:7">
@@ -2943,10 +3061,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>10</v>
@@ -2957,9 +3075,8 @@
       <c r="F29" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B29,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G29" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" customFormat="1" spans="1:7">
@@ -2967,10 +3084,10 @@
         <v>7</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>10</v>
@@ -2981,9 +3098,8 @@
       <c r="F30" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G30" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B30,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G30" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31" customFormat="1" spans="1:7">
@@ -2991,10 +3107,10 @@
         <v>7</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>10</v>
@@ -3005,9 +3121,8 @@
       <c r="F31" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G31" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B31,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G31" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:7">
@@ -3015,10 +3130,10 @@
         <v>7</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>10</v>
@@ -3029,9 +3144,8 @@
       <c r="F32" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G32" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B32,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G32" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="1:7">
@@ -3039,10 +3153,10 @@
         <v>7</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>10</v>
@@ -3053,9 +3167,8 @@
       <c r="F33" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G33" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B33,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G33" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="1" spans="1:7">
@@ -3063,10 +3176,10 @@
         <v>7</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>10</v>
@@ -3077,9 +3190,8 @@
       <c r="F34" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G34" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B34,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G34" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="35" customFormat="1" spans="1:7">
@@ -3087,10 +3199,10 @@
         <v>7</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>10</v>
@@ -3101,9 +3213,8 @@
       <c r="F35" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G35" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B35,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G35" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="36" customFormat="1" spans="1:7">
@@ -3111,10 +3222,10 @@
         <v>7</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>10</v>
@@ -3125,9 +3236,8 @@
       <c r="F36" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B36,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G36" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="37" customFormat="1" spans="1:7">
@@ -3135,10 +3245,10 @@
         <v>7</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D37" s="15" t="s">
         <v>10</v>
@@ -3149,9 +3259,8 @@
       <c r="F37" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B37,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G37" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="38" customFormat="1" spans="1:7">
@@ -3159,10 +3268,10 @@
         <v>7</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>10</v>
@@ -3173,9 +3282,8 @@
       <c r="F38" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B38,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G38" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:7">
@@ -3183,10 +3291,10 @@
         <v>7</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D39" s="15" t="s">
         <v>10</v>
@@ -3197,9 +3305,8 @@
       <c r="F39" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B39,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G39" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="40" customFormat="1" spans="1:7">
@@ -3207,10 +3314,10 @@
         <v>7</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>10</v>
@@ -3221,9 +3328,8 @@
       <c r="F40" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B40,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G40" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="1" spans="1:7">
@@ -3231,10 +3337,10 @@
         <v>7</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>10</v>
@@ -3245,9 +3351,8 @@
       <c r="F41" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B41,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G41" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
@@ -3255,10 +3360,10 @@
         <v>7</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>10</v>
@@ -3269,9 +3374,8 @@
       <c r="F42" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G42" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B42,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G42" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="43" customFormat="1" spans="1:7">
@@ -3279,10 +3383,10 @@
         <v>7</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>10</v>
@@ -3293,9 +3397,8 @@
       <c r="F43" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B43,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G43" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="44" customFormat="1" spans="1:7">
@@ -3303,10 +3406,10 @@
         <v>7</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>10</v>
@@ -3317,9 +3420,8 @@
       <c r="F44" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G44" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B44,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G44" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:7">
@@ -3327,10 +3429,10 @@
         <v>7</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>10</v>
@@ -3341,9 +3443,8 @@
       <c r="F45" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G45" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B45,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G45" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="46" customFormat="1" spans="1:7">
@@ -3351,10 +3452,10 @@
         <v>7</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>10</v>
@@ -3365,9 +3466,8 @@
       <c r="F46" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G46" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B46,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G46" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="47" customFormat="1" spans="1:7">
@@ -3375,10 +3475,10 @@
         <v>7</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>10</v>
@@ -3389,20 +3489,19 @@
       <c r="F47" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G47" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B47,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G47" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="1" spans="1:7">
       <c r="A48" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B48" s="15" t="s">
-        <v>103</v>
+      <c r="B48" t="s">
+        <v>105</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>10</v>
@@ -3413,9 +3512,8 @@
       <c r="F48" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G48" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B48,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G48" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="49" customFormat="1" spans="1:7">
@@ -3423,10 +3521,10 @@
         <v>7</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>10</v>
@@ -3437,9 +3535,8 @@
       <c r="F49" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G49" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B49,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G49" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="50" customFormat="1" spans="1:7">
@@ -3447,10 +3544,10 @@
         <v>7</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>10</v>
@@ -3461,9 +3558,8 @@
       <c r="F50" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G50" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B50,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G50" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="51" customFormat="1" spans="1:7">
@@ -3471,10 +3567,10 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D51" s="15" t="s">
         <v>10</v>
@@ -3485,9 +3581,8 @@
       <c r="F51" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B51,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G51" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="52" customFormat="1" spans="1:7">
@@ -3495,10 +3590,10 @@
         <v>7</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>10</v>
@@ -3509,9 +3604,8 @@
       <c r="F52" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G52" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B52,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G52" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -3519,10 +3613,10 @@
         <v>7</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>10</v>
@@ -3533,9 +3627,8 @@
       <c r="F53" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B53,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G53" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -3543,10 +3636,10 @@
         <v>7</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D54" s="15" t="s">
         <v>10</v>
@@ -3557,9 +3650,8 @@
       <c r="F54" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G54" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B54,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G54" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -3567,10 +3659,10 @@
         <v>7</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>10</v>
@@ -3581,9 +3673,8 @@
       <c r="F55" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B55,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G55" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:7">
@@ -3591,10 +3682,10 @@
         <v>7</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>10</v>
@@ -3605,9 +3696,8 @@
       <c r="F56" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G56" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B56,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G56" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="57" customFormat="1" spans="1:7">
@@ -3615,10 +3705,10 @@
         <v>7</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>10</v>
@@ -3629,9 +3719,8 @@
       <c r="F57" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G57" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B57,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G57" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="58" customFormat="1" spans="1:7">
@@ -3639,10 +3728,10 @@
         <v>7</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D58" s="15" t="s">
         <v>10</v>
@@ -3653,20 +3742,19 @@
       <c r="F58" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B58,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G58" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
       <c r="A59" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="15" t="s">
-        <v>125</v>
+      <c r="B59" t="s">
+        <v>127</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D59" s="15" t="s">
         <v>10</v>
@@ -3677,9 +3765,8 @@
       <c r="F59" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G59" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B59,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G59" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -3687,10 +3774,10 @@
         <v>7</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>10</v>
@@ -3701,9 +3788,8 @@
       <c r="F60" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G60" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B60,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G60" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:7">
@@ -3711,10 +3797,10 @@
         <v>7</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D61" s="15" t="s">
         <v>10</v>
@@ -3725,9 +3811,8 @@
       <c r="F61" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G61" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B61,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G61" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="1" spans="1:7">
@@ -3735,10 +3820,10 @@
         <v>7</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>10</v>
@@ -3749,9 +3834,8 @@
       <c r="F62" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G62" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B62,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G62" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="63" customFormat="1" spans="1:7">
@@ -3759,10 +3843,10 @@
         <v>7</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>10</v>
@@ -3773,9 +3857,8 @@
       <c r="F63" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G63" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B63,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G63" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="64" customFormat="1" spans="1:7">
@@ -3783,10 +3866,10 @@
         <v>7</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>10</v>
@@ -3797,9 +3880,8 @@
       <c r="F64" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G64" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B64,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G64" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="65" customFormat="1" spans="1:7">
@@ -3807,10 +3889,10 @@
         <v>7</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D65" s="15" t="s">
         <v>10</v>
@@ -3821,9 +3903,8 @@
       <c r="F65" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G65" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B65,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G65" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="66" customFormat="1" spans="1:7">
@@ -3831,10 +3912,10 @@
         <v>7</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>10</v>
@@ -3845,9 +3926,8 @@
       <c r="F66" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G66" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B66,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G66" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="67" customFormat="1" spans="1:7">
@@ -3855,10 +3935,10 @@
         <v>7</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D67" s="15" t="s">
         <v>10</v>
@@ -3869,9 +3949,8 @@
       <c r="F67" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G67" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B67,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G67" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="68" customFormat="1" spans="1:7">
@@ -3879,10 +3958,10 @@
         <v>7</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>10</v>
@@ -3893,9 +3972,8 @@
       <c r="F68" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G68" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B68,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G68" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -3903,10 +3981,10 @@
         <v>7</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D69" s="15" t="s">
         <v>10</v>
@@ -3917,9 +3995,8 @@
       <c r="F69" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G69" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B69,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G69" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -3927,10 +4004,10 @@
         <v>7</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>10</v>
@@ -3941,9 +4018,8 @@
       <c r="F70" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G70" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B70,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G70" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:7">
@@ -3951,10 +4027,10 @@
         <v>7</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D71" s="15" t="s">
         <v>10</v>
@@ -3965,9 +4041,8 @@
       <c r="F71" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G71" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B71,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G71" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="72" customFormat="1" spans="1:7">
@@ -3975,10 +4050,10 @@
         <v>7</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D72" s="15" t="s">
         <v>10</v>
@@ -3989,9 +4064,8 @@
       <c r="F72" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G72" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B72,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G72" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="73" customFormat="1" spans="1:7">
@@ -3999,10 +4073,10 @@
         <v>7</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D73" s="15" t="s">
         <v>10</v>
@@ -4013,9 +4087,8 @@
       <c r="F73" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G73" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B73,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G73" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="74" customFormat="1" spans="1:7">
@@ -4023,10 +4096,10 @@
         <v>7</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>10</v>
@@ -4037,9 +4110,8 @@
       <c r="F74" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G74" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B74,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G74" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="75" customFormat="1" spans="1:7">
@@ -4047,10 +4119,10 @@
         <v>7</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D75" s="15" t="s">
         <v>10</v>
@@ -4061,9 +4133,8 @@
       <c r="F75" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G75" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B75,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G75" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="76" customFormat="1" spans="1:7">
@@ -4071,10 +4142,10 @@
         <v>7</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>10</v>
@@ -4085,9 +4156,8 @@
       <c r="F76" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G76" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B76,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G76" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="77" customFormat="1" spans="1:7">
@@ -4095,10 +4165,10 @@
         <v>7</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D77" s="15" t="s">
         <v>10</v>
@@ -4109,9 +4179,8 @@
       <c r="F77" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G77" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B77,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G77" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="78" customFormat="1" spans="1:7">
@@ -4119,10 +4188,10 @@
         <v>7</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>10</v>
@@ -4133,9 +4202,8 @@
       <c r="F78" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G78" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B78,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G78" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="79" customFormat="1" spans="1:7">
@@ -4143,10 +4211,10 @@
         <v>7</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D79" s="15" t="s">
         <v>10</v>
@@ -4157,9 +4225,8 @@
       <c r="F79" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G79" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B79,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G79" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="80" customFormat="1" spans="1:7">
@@ -4167,10 +4234,10 @@
         <v>7</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>10</v>
@@ -4181,9 +4248,8 @@
       <c r="F80" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G80" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B80,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G80" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="81" customFormat="1" spans="1:7">
@@ -4191,10 +4257,10 @@
         <v>7</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D81" s="15" t="s">
         <v>10</v>
@@ -4205,9 +4271,8 @@
       <c r="F81" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G81" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B81,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G81" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -4215,10 +4280,10 @@
         <v>7</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>10</v>
@@ -4229,9 +4294,8 @@
       <c r="F82" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G82" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B82,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G82" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -4239,10 +4303,10 @@
         <v>7</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D83" s="15" t="s">
         <v>10</v>
@@ -4253,9 +4317,8 @@
       <c r="F83" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G83" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B83,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G83" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -4263,10 +4326,10 @@
         <v>7</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>10</v>
@@ -4277,9 +4340,8 @@
       <c r="F84" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G84" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B84,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G84" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:7">
@@ -4287,10 +4349,10 @@
         <v>7</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D85" s="15" t="s">
         <v>10</v>
@@ -4301,9 +4363,8 @@
       <c r="F85" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G85" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B85,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G85" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="86" customFormat="1" spans="1:7">
@@ -4311,10 +4372,10 @@
         <v>7</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>10</v>
@@ -4326,7 +4387,7 @@
         <v>12</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" customFormat="1" spans="1:7">
@@ -4334,10 +4395,10 @@
         <v>7</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D87" s="15" t="s">
         <v>10</v>
@@ -4348,9 +4409,8 @@
       <c r="F87" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G87" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B87,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G87" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="88" customFormat="1" spans="1:7">
@@ -4358,10 +4418,10 @@
         <v>7</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>10</v>
@@ -4373,7 +4433,7 @@
         <v>12</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" customFormat="1" spans="1:7">
@@ -4381,10 +4441,10 @@
         <v>7</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D89" s="15" t="s">
         <v>10</v>
@@ -4395,9 +4455,8 @@
       <c r="F89" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G89" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B89,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G89" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="90" customFormat="1" spans="1:7">
@@ -4405,10 +4464,10 @@
         <v>7</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>10</v>
@@ -4419,9 +4478,8 @@
       <c r="F90" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G90" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B90,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G90" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="91" customFormat="1" spans="1:7">
@@ -4429,10 +4487,10 @@
         <v>7</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D91" s="15" t="s">
         <v>10</v>
@@ -4443,9 +4501,8 @@
       <c r="F91" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G91" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B91,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G91" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="92" customFormat="1" spans="1:7">
@@ -4453,10 +4510,10 @@
         <v>7</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>10</v>
@@ -4467,9 +4524,8 @@
       <c r="F92" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G92" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B92,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G92" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:7">
@@ -4477,10 +4533,10 @@
         <v>7</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D93" s="15" t="s">
         <v>10</v>
@@ -4491,9 +4547,8 @@
       <c r="F93" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G93" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B93,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G93" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -4501,10 +4556,10 @@
         <v>7</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>10</v>
@@ -4515,9 +4570,8 @@
       <c r="F94" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G94" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B94,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G94" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:7">
@@ -4525,10 +4579,10 @@
         <v>7</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D95" s="15" t="s">
         <v>10</v>
@@ -4539,9 +4593,8 @@
       <c r="F95" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B95,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G95" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="96" customFormat="1" spans="1:7">
@@ -4549,10 +4602,10 @@
         <v>7</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>10</v>
@@ -4563,9 +4616,8 @@
       <c r="F96" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G96" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B96,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G96" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="97" customFormat="1" spans="1:7">
@@ -4573,10 +4625,10 @@
         <v>7</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D97" s="15" t="s">
         <v>10</v>
@@ -4587,9 +4639,8 @@
       <c r="F97" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G97" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B97,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G97" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="98" customFormat="1" spans="1:7">
@@ -4597,10 +4648,10 @@
         <v>7</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>10</v>
@@ -4611,9 +4662,8 @@
       <c r="F98" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G98" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B98,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G98" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="99" customFormat="1" spans="1:7">
@@ -4621,10 +4671,10 @@
         <v>7</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D99" s="15" t="s">
         <v>10</v>
@@ -4635,9 +4685,8 @@
       <c r="F99" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G99" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B99,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G99" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="100" customFormat="1" spans="1:7">
@@ -4645,10 +4694,10 @@
         <v>7</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>10</v>
@@ -4659,9 +4708,8 @@
       <c r="F100" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G100" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B100,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G100" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="101" customFormat="1" spans="1:7">
@@ -4669,10 +4717,10 @@
         <v>7</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D101" s="15" t="s">
         <v>10</v>
@@ -4683,9 +4731,8 @@
       <c r="F101" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G101" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B101,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G101" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="102" customFormat="1" spans="1:7">
@@ -4693,10 +4740,10 @@
         <v>7</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>10</v>
@@ -4707,9 +4754,8 @@
       <c r="F102" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G102" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B102,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G102" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="103" customFormat="1" spans="1:7">
@@ -4717,10 +4763,10 @@
         <v>7</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D103" s="15" t="s">
         <v>10</v>
@@ -4731,9 +4777,8 @@
       <c r="F103" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G103" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B103,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G103" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -4741,10 +4786,10 @@
         <v>7</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>10</v>
@@ -4755,9 +4800,8 @@
       <c r="F104" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G104" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B104,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G104" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -4765,10 +4809,10 @@
         <v>7</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D105" s="15" t="s">
         <v>10</v>
@@ -4779,9 +4823,8 @@
       <c r="F105" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G105" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B105,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G105" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:7">
@@ -4789,10 +4832,10 @@
         <v>7</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>10</v>
@@ -4803,9 +4846,8 @@
       <c r="F106" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G106" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B106,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G106" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="107" customFormat="1" spans="1:7">
@@ -4813,10 +4855,10 @@
         <v>7</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D107" s="15" t="s">
         <v>10</v>
@@ -4827,9 +4869,8 @@
       <c r="F107" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G107" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B107,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G107" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="108" customFormat="1" spans="1:7">
@@ -4837,10 +4878,10 @@
         <v>7</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>10</v>
@@ -4851,9 +4892,8 @@
       <c r="F108" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G108" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B108,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G108" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="109" customFormat="1" spans="1:7">
@@ -4861,10 +4901,10 @@
         <v>7</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D109" s="15" t="s">
         <v>10</v>
@@ -4875,9 +4915,8 @@
       <c r="F109" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G109" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B109,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G109" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="110" customFormat="1" spans="1:7">
@@ -4885,10 +4924,10 @@
         <v>7</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>10</v>
@@ -4900,7 +4939,7 @@
         <v>12</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" customFormat="1" spans="1:7">
@@ -4908,10 +4947,10 @@
         <v>7</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D111" s="15" t="s">
         <v>10</v>
@@ -4922,9 +4961,8 @@
       <c r="F111" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G111" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B111,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G111" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="112" customFormat="1" spans="1:7">
@@ -4932,10 +4970,10 @@
         <v>7</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>10</v>
@@ -4946,9 +4984,8 @@
       <c r="F112" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G112" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B112,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G112" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="113" customFormat="1" spans="1:7">
@@ -4956,10 +4993,10 @@
         <v>7</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D113" s="15" t="s">
         <v>10</v>
@@ -4970,9 +5007,8 @@
       <c r="F113" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G113" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B113,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G113" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="114" customFormat="1" spans="1:7">
@@ -4980,10 +5016,10 @@
         <v>7</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>10</v>
@@ -4994,9 +5030,8 @@
       <c r="F114" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G114" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B114,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G114" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="115" customFormat="1" spans="1:7">
@@ -5004,10 +5039,10 @@
         <v>7</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>10</v>
@@ -5018,9 +5053,8 @@
       <c r="F115" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G115" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B115,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G115" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="116" customFormat="1" spans="1:7">
@@ -5028,10 +5062,10 @@
         <v>7</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>10</v>
@@ -5042,9 +5076,8 @@
       <c r="F116" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G116" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B116,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G116" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="117" customFormat="1" spans="1:7">
@@ -5052,10 +5085,10 @@
         <v>7</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D117" s="15" t="s">
         <v>10</v>
@@ -5066,9 +5099,8 @@
       <c r="F117" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G117" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B117,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G117" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:7">
@@ -5076,10 +5108,10 @@
         <v>7</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>10</v>
@@ -5090,9 +5122,8 @@
       <c r="F118" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G118" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B118,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G118" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:7">
@@ -5100,10 +5131,10 @@
         <v>7</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D119" s="15" t="s">
         <v>10</v>
@@ -5114,9 +5145,8 @@
       <c r="F119" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G119" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B119,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G119" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:7">
@@ -5124,10 +5154,10 @@
         <v>7</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>10</v>
@@ -5138,9 +5168,8 @@
       <c r="F120" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G120" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B120,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G120" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="121" customFormat="1" spans="1:7">
@@ -5148,10 +5177,10 @@
         <v>7</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>10</v>
@@ -5162,9 +5191,8 @@
       <c r="F121" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G121" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B121,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>off</v>
+      <c r="G121" s="15" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -5172,10 +5200,10 @@
         <v>7</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>10</v>
@@ -5186,9 +5214,8 @@
       <c r="F122" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G122" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B122,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G122" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:7">
@@ -5196,10 +5223,10 @@
         <v>7</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D123" s="15" t="s">
         <v>10</v>
@@ -5210,9 +5237,8 @@
       <c r="F123" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G123" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B123,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G123" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:7">
@@ -5220,10 +5246,10 @@
         <v>7</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>10</v>
@@ -5234,9 +5260,8 @@
       <c r="F124" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G124" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B124,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G124" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="125" customFormat="1" spans="1:7">
@@ -5244,10 +5269,10 @@
         <v>7</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D125" s="15" t="s">
         <v>10</v>
@@ -5258,9 +5283,8 @@
       <c r="F125" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G125" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B125,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G125" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:7">
@@ -5268,10 +5292,10 @@
         <v>7</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>10</v>
@@ -5283,7 +5307,7 @@
         <v>12</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -5291,10 +5315,10 @@
         <v>7</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D127" s="15" t="s">
         <v>10</v>
@@ -5305,9 +5329,8 @@
       <c r="F127" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G127" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B127,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G127" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="128" customFormat="1" spans="1:7">
@@ -5315,10 +5338,10 @@
         <v>7</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>10</v>
@@ -5329,9 +5352,8 @@
       <c r="F128" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G128" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B128,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G128" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:7">
@@ -5339,10 +5361,10 @@
         <v>7</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D129" s="15" t="s">
         <v>10</v>
@@ -5353,9 +5375,8 @@
       <c r="F129" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G129" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B129,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G129" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:7">
@@ -5363,10 +5384,10 @@
         <v>7</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>10</v>
@@ -5377,9 +5398,8 @@
       <c r="F130" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G130" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B130,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G130" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="131" customFormat="1" spans="1:7">
@@ -5387,10 +5407,10 @@
         <v>7</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D131" s="15" t="s">
         <v>10</v>
@@ -5401,9 +5421,8 @@
       <c r="F131" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G131" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B131,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G131" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="132" customFormat="1" spans="1:7">
@@ -5411,10 +5430,10 @@
         <v>7</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>10</v>
@@ -5425,9 +5444,8 @@
       <c r="F132" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G132" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B132,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G132" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="133" customFormat="1" spans="1:7">
@@ -5435,10 +5453,10 @@
         <v>7</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>10</v>
@@ -5449,9 +5467,8 @@
       <c r="F133" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G133" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B133,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G133" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="134" customFormat="1" spans="1:7">
@@ -5459,10 +5476,10 @@
         <v>7</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>10</v>
@@ -5473,9 +5490,8 @@
       <c r="F134" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G134" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B134,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G134" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:7">
@@ -5483,10 +5499,10 @@
         <v>7</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D135" s="15" t="s">
         <v>10</v>
@@ -5497,9 +5513,8 @@
       <c r="F135" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G135" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B135,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G135" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:7">
@@ -5507,10 +5522,10 @@
         <v>7</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>10</v>
@@ -5521,9 +5536,8 @@
       <c r="F136" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G136" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B136,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G136" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:7">
@@ -5531,10 +5545,10 @@
         <v>7</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D137" s="15" t="s">
         <v>10</v>
@@ -5545,9 +5559,8 @@
       <c r="F137" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G137" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B137,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G137" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:7">
@@ -5555,10 +5568,10 @@
         <v>7</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>10</v>
@@ -5569,9 +5582,8 @@
       <c r="F138" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G138" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B138,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G138" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="139" customFormat="1" spans="1:7">
@@ -5579,10 +5591,10 @@
         <v>7</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D139" s="15" t="s">
         <v>10</v>
@@ -5593,9 +5605,8 @@
       <c r="F139" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G139" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B139,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G139" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="140" customFormat="1" spans="1:7">
@@ -5603,10 +5614,10 @@
         <v>7</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>10</v>
@@ -5617,9 +5628,8 @@
       <c r="F140" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G140" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B140,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G140" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="141" customFormat="1" spans="1:7">
@@ -5627,10 +5637,10 @@
         <v>7</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D141" s="15" t="s">
         <v>10</v>
@@ -5641,9 +5651,8 @@
       <c r="F141" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G141" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B141,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G141" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:7">
@@ -5651,10 +5660,10 @@
         <v>7</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>10</v>
@@ -5665,9 +5674,8 @@
       <c r="F142" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G142" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B142,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G142" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="143" customFormat="1" spans="1:7">
@@ -5675,10 +5683,10 @@
         <v>7</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D143" s="15" t="s">
         <v>10</v>
@@ -5689,9 +5697,8 @@
       <c r="F143" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G143" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B143,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G143" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="144" customFormat="1" spans="1:7">
@@ -5699,10 +5706,10 @@
         <v>7</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>10</v>
@@ -5713,9 +5720,8 @@
       <c r="F144" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G144" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B144,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G144" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="145" customFormat="1" spans="1:7">
@@ -5723,10 +5729,10 @@
         <v>7</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D145" s="15" t="s">
         <v>10</v>
@@ -5737,9 +5743,8 @@
       <c r="F145" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G145" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B145,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G145" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="146" customFormat="1" spans="1:7">
@@ -5747,10 +5752,10 @@
         <v>7</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>10</v>
@@ -5761,9 +5766,8 @@
       <c r="F146" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G146" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B146,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G146" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="147" customFormat="1" spans="1:7">
@@ -5771,10 +5775,10 @@
         <v>7</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D147" s="15" t="s">
         <v>10</v>
@@ -5785,20 +5789,19 @@
       <c r="F147" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G147" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B147,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
-      </c>
-    </row>
-    <row r="148" customFormat="1" spans="1:7">
+      <c r="G147" s="15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" ht="15.15" spans="1:7">
       <c r="A148" s="15" t="s">
         <v>7</v>
       </c>
       <c r="B148" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>10</v>
@@ -5809,44 +5812,42 @@
       <c r="F148" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G148" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B148,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="G148" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="149" customFormat="1" spans="1:7">
-      <c r="A149" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B149" s="15" t="s">
-        <v>290</v>
-      </c>
-      <c r="C149" s="15" t="s">
-        <v>306</v>
-      </c>
-      <c r="D149" s="15" t="s">
+      <c r="A149" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B149" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="D149" s="20" t="s">
         <v>10</v>
       </c>
       <c r="E149" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F149" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G149" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B149,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="F149" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G149" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="150" customFormat="1" spans="1:7">
       <c r="A150" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B150" s="15" t="s">
-        <v>292</v>
+      <c r="B150" s="19" t="s">
+        <v>293</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>10</v>
@@ -5854,23 +5855,22 @@
       <c r="E150" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F150" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G150" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B150,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="F150" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="151" customFormat="1" spans="1:7">
       <c r="A151" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B151" s="15" t="s">
-        <v>296</v>
+      <c r="B151" s="19" t="s">
+        <v>297</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D151" s="15" t="s">
         <v>10</v>
@@ -5878,23 +5878,22 @@
       <c r="E151" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F151" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G151" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B151,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="F151" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="152" customFormat="1" spans="1:7">
       <c r="A152" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B152" s="15" t="s">
-        <v>254</v>
+      <c r="B152" s="19" t="s">
+        <v>255</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>10</v>
@@ -5902,23 +5901,22 @@
       <c r="E152" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F152" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G152" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B152,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="F152" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="153" customFormat="1" spans="1:7">
       <c r="A153" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B153" s="15" t="s">
-        <v>192</v>
+      <c r="B153" s="19" t="s">
+        <v>193</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D153" s="15" t="s">
         <v>10</v>
@@ -5926,23 +5924,22 @@
       <c r="E153" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F153" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G153" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B153,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="F153" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G153" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="154" customFormat="1" spans="1:7">
       <c r="A154" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B154" s="15" t="s">
-        <v>256</v>
+      <c r="B154" s="19" t="s">
+        <v>257</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D154" s="15" t="s">
         <v>10</v>
@@ -5950,23 +5947,22 @@
       <c r="E154" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F154" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G154" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B154,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="F154" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G154" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="155" customFormat="1" spans="1:7">
       <c r="A155" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B155" s="15" t="s">
-        <v>77</v>
+      <c r="B155" s="19" t="s">
+        <v>79</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>10</v>
@@ -5974,23 +5970,22 @@
       <c r="E155" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F155" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G155" s="15" t="str">
-        <f>IF(ISNUMBER(MATCH(B155,Sheet3!$A:$A,0)),"on","off")</f>
-        <v>on</v>
+      <c r="F155" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G155" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="156" customFormat="1" spans="1:7">
       <c r="A156" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B156" s="15" t="s">
-        <v>313</v>
+      <c r="B156" s="19" t="s">
+        <v>314</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>10</v>
@@ -5998,22 +5993,22 @@
       <c r="E156" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F156" s="17" t="s">
+      <c r="F156" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" customFormat="1" spans="1:7">
       <c r="A157" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B157" s="15" t="s">
-        <v>315</v>
+      <c r="B157" s="19" t="s">
+        <v>316</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D157" s="15" t="s">
         <v>10</v>
@@ -6021,22 +6016,22 @@
       <c r="E157" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F157" s="17" t="s">
+      <c r="F157" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G157" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158" customFormat="1" spans="1:7">
       <c r="A158" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B158" s="15" t="s">
-        <v>317</v>
+      <c r="B158" s="19" t="s">
+        <v>318</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>10</v>
@@ -6044,22 +6039,22 @@
       <c r="E158" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F158" s="17" t="s">
+      <c r="F158" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159" customFormat="1" spans="1:7">
       <c r="A159" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B159" s="15" t="s">
-        <v>319</v>
+      <c r="B159" s="19" t="s">
+        <v>320</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D159" s="15" t="s">
         <v>10</v>
@@ -6067,22 +6062,22 @@
       <c r="E159" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F159" s="17" t="s">
+      <c r="F159" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G159" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" customFormat="1" spans="1:7">
       <c r="A160" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B160" s="15" t="s">
-        <v>321</v>
+      <c r="B160" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D160" s="15" t="s">
         <v>10</v>
@@ -6090,22 +6085,22 @@
       <c r="E160" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F160" s="17" t="s">
+      <c r="F160" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" customFormat="1" spans="1:7">
       <c r="A161" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B161" s="15" t="s">
-        <v>323</v>
+      <c r="B161" s="19" t="s">
+        <v>324</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D161" s="15" t="s">
         <v>10</v>
@@ -6113,22 +6108,22 @@
       <c r="E161" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F161" s="17" t="s">
+      <c r="F161" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G161" s="15" t="s">
-        <v>181</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162" customFormat="1" spans="1:7">
       <c r="A162" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B162" s="15" t="s">
-        <v>325</v>
+      <c r="B162" s="19" t="s">
+        <v>326</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>10</v>
@@ -6136,22 +6131,22 @@
       <c r="E162" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F162" s="17" t="s">
+      <c r="F162" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" customFormat="1" spans="1:7">
       <c r="A163" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B163" s="15" t="s">
-        <v>327</v>
+      <c r="B163" s="19" t="s">
+        <v>328</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D163" s="15" t="s">
         <v>10</v>
@@ -6159,22 +6154,22 @@
       <c r="E163" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F163" s="17" t="s">
+      <c r="F163" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G163" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" customFormat="1" spans="1:7">
       <c r="A164" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B164" s="15" t="s">
-        <v>329</v>
+      <c r="B164" s="19" t="s">
+        <v>330</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>10</v>
@@ -6182,22 +6177,22 @@
       <c r="E164" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F164" s="17" t="s">
+      <c r="F164" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" customFormat="1" spans="1:7">
       <c r="A165" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B165" s="15" t="s">
-        <v>331</v>
+      <c r="B165" s="19" t="s">
+        <v>332</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D165" s="15" t="s">
         <v>10</v>
@@ -6205,34 +6200,34 @@
       <c r="E165" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F165" s="17" t="s">
+      <c r="F165" s="15" t="s">
         <v>12</v>
       </c>
       <c r="G165" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="166" customFormat="1" spans="1:7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" customFormat="1" ht="28.8" spans="1:7">
       <c r="A166" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B166" s="15" t="s">
-        <v>333</v>
+      <c r="B166" s="19" t="s">
+        <v>334</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E166" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F166" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G166" s="20" t="s">
-        <v>181</v>
+      <c r="E166" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166" s="15" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:7">
@@ -6240,10 +6235,10 @@
         <v>7</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="D167" s="15" t="s">
         <v>10</v>
@@ -6254,8 +6249,8 @@
       <c r="F167" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G167" s="20" t="s">
-        <v>181</v>
+      <c r="G167" s="24" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:7">
@@ -6263,10 +6258,10 @@
         <v>7</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>10</v>
@@ -6277,8 +6272,8 @@
       <c r="F168" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G168" s="20" t="s">
-        <v>181</v>
+      <c r="G168" s="24" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="169" customFormat="1" spans="1:7">
@@ -6286,10 +6281,10 @@
         <v>7</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="D169" s="15" t="s">
         <v>10</v>
@@ -6300,8 +6295,8 @@
       <c r="F169" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G169" s="20" t="s">
-        <v>181</v>
+      <c r="G169" s="24" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="170" customFormat="1" spans="1:7">
@@ -6309,10 +6304,10 @@
         <v>7</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="D170" s="15" t="s">
         <v>10</v>
@@ -6323,8 +6318,8 @@
       <c r="F170" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G170" s="20" t="s">
-        <v>181</v>
+      <c r="G170" s="24" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:7">
@@ -6332,10 +6327,10 @@
         <v>7</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D171" s="15" t="s">
         <v>10</v>
@@ -6346,8 +6341,8 @@
       <c r="F171" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G171" s="20" t="s">
-        <v>181</v>
+      <c r="G171" s="24" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:7">
@@ -6355,10 +6350,10 @@
         <v>7</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>10</v>
@@ -6369,135 +6364,331 @@
       <c r="F172" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G172" s="20" t="s">
-        <v>181</v>
+      <c r="G172" s="24" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:7">
-      <c r="A173" s="15"/>
-      <c r="B173" s="15"/>
-      <c r="C173" s="15"/>
-      <c r="D173" s="15"/>
-      <c r="E173" s="15"/>
-      <c r="F173" s="17"/>
-      <c r="G173" s="15"/>
+      <c r="A173" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C173" s="15" t="s">
+        <v>348</v>
+      </c>
+      <c r="D173" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E173" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G173" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="174" customFormat="1" spans="1:7">
-      <c r="A174" s="15"/>
-      <c r="B174" s="15"/>
-      <c r="C174" s="15"/>
-      <c r="D174" s="15"/>
-      <c r="E174" s="15"/>
-      <c r="F174" s="17"/>
-      <c r="G174" s="15"/>
+      <c r="A174" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="C174" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="D174" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E174" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G174" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="175" customFormat="1" spans="1:7">
-      <c r="A175" s="15"/>
-      <c r="B175" s="15"/>
-      <c r="C175" s="15"/>
-      <c r="D175" s="15"/>
-      <c r="E175" s="15"/>
-      <c r="F175" s="17"/>
-      <c r="G175" s="15"/>
+      <c r="A175" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B175" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="C175" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="D175" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G175" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="176" customFormat="1" spans="1:7">
-      <c r="A176" s="15"/>
-      <c r="B176" s="15"/>
-      <c r="C176" s="15"/>
-      <c r="D176" s="15"/>
-      <c r="E176" s="15"/>
-      <c r="F176" s="17"/>
-      <c r="G176" s="15"/>
+      <c r="A176" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="C176" s="15" t="s">
+        <v>354</v>
+      </c>
+      <c r="D176" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E176" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G176" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="177" customFormat="1" spans="1:7">
-      <c r="A177" s="15"/>
-      <c r="B177" s="15"/>
-      <c r="C177" s="15"/>
-      <c r="D177" s="15"/>
-      <c r="E177" s="15"/>
-      <c r="F177" s="17"/>
-      <c r="G177" s="15"/>
+      <c r="A177" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B177" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="C177" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="D177" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E177" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G177" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="178" customFormat="1" spans="1:7">
-      <c r="A178" s="15"/>
-      <c r="B178" s="15"/>
-      <c r="C178" s="15"/>
-      <c r="D178" s="15"/>
-      <c r="E178" s="15"/>
-      <c r="F178" s="17"/>
-      <c r="G178" s="15"/>
+      <c r="A178" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="C178" s="15" t="s">
+        <v>358</v>
+      </c>
+      <c r="D178" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E178" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G178" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="179" customFormat="1" spans="1:7">
-      <c r="A179" s="15"/>
-      <c r="B179" s="15"/>
-      <c r="C179" s="15"/>
-      <c r="D179" s="15"/>
-      <c r="E179" s="15"/>
-      <c r="F179" s="17"/>
-      <c r="G179" s="15"/>
+      <c r="A179" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B179" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C179" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="D179" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E179" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G179" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="180" customFormat="1" spans="1:7">
-      <c r="A180" s="15"/>
-      <c r="B180" s="15"/>
-      <c r="C180" s="15"/>
-      <c r="D180" s="15"/>
-      <c r="E180" s="15"/>
-      <c r="F180" s="17"/>
-      <c r="G180" s="15"/>
+      <c r="A180" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B180" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="C180" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="D180" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E180" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G180" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="181" customFormat="1" spans="1:7">
-      <c r="A181" s="15"/>
-      <c r="B181" s="15"/>
-      <c r="C181" s="15"/>
-      <c r="D181" s="15"/>
-      <c r="E181" s="15"/>
-      <c r="F181" s="17"/>
-      <c r="G181" s="15"/>
+      <c r="A181" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B181" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="C181" s="15" t="s">
+        <v>364</v>
+      </c>
+      <c r="D181" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G181" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="182" customFormat="1" spans="1:7">
-      <c r="A182" s="15"/>
-      <c r="B182" s="15"/>
-      <c r="C182" s="15"/>
-      <c r="D182" s="15"/>
-      <c r="E182" s="15"/>
-      <c r="F182" s="17"/>
-      <c r="G182" s="15"/>
+      <c r="A182" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B182" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="C182" s="15" t="s">
+        <v>366</v>
+      </c>
+      <c r="D182" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E182" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G182" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="183" customFormat="1" spans="1:7">
-      <c r="A183" s="15"/>
-      <c r="B183" s="15"/>
-      <c r="C183" s="15"/>
-      <c r="D183" s="15"/>
-      <c r="E183" s="15"/>
-      <c r="F183" s="17"/>
-      <c r="G183" s="15"/>
+      <c r="A183" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B183" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="C183" s="15" t="s">
+        <v>368</v>
+      </c>
+      <c r="D183" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E183" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G183" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="184" customFormat="1" spans="1:7">
-      <c r="A184" s="15"/>
-      <c r="B184" s="15"/>
-      <c r="C184" s="15"/>
-      <c r="D184" s="15"/>
-      <c r="E184" s="15"/>
-      <c r="F184" s="17"/>
-      <c r="G184" s="15"/>
+      <c r="A184" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C184" s="15" t="s">
+        <v>370</v>
+      </c>
+      <c r="D184" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E184" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G184" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="185" customFormat="1" spans="1:7">
-      <c r="A185" s="15"/>
-      <c r="B185" s="15"/>
-      <c r="C185" s="15"/>
-      <c r="D185" s="15"/>
-      <c r="E185" s="15"/>
-      <c r="F185" s="17"/>
-      <c r="G185" s="15"/>
+      <c r="A185" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="C185" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="D185" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E185" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G185" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="186" customFormat="1" spans="1:7">
-      <c r="A186" s="15"/>
-      <c r="B186" s="15"/>
-      <c r="C186" s="15"/>
-      <c r="D186" s="15"/>
-      <c r="E186" s="15"/>
-      <c r="F186" s="17"/>
-      <c r="G186" s="15"/>
+      <c r="A186" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B186" s="15" t="s">
+        <v>373</v>
+      </c>
+      <c r="C186" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="D186" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E186" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G186" s="24" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="187" customFormat="1" spans="1:7">
       <c r="A187" s="15"/>
@@ -6823,8 +7014,17 @@
       <c r="F222" s="17"/>
       <c r="G222" s="15"/>
     </row>
+    <row r="223" customFormat="1" spans="1:7">
+      <c r="A223" s="15"/>
+      <c r="B223" s="15"/>
+      <c r="C223" s="15"/>
+      <c r="D223" s="15"/>
+      <c r="E223" s="15"/>
+      <c r="F223" s="17"/>
+      <c r="G223" s="15"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G171" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G174" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B128">
@@ -6925,297 +7125,297 @@
   <sheetData>
     <row r="1" s="3" customFormat="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>343</v>
+        <v>376</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>344</v>
+        <v>377</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>345</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" s="3" customFormat="1" spans="1:5">
       <c r="A5" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" ht="77" customHeight="1" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>351</v>
+        <v>384</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>352</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" spans="1:5">
       <c r="A8" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" s="3" customFormat="1" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>346</v>
+        <v>379</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" s="3" customFormat="1" spans="1:5">
       <c r="A14" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:5">
       <c r="A16" s="6" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9" t="s">
-        <v>355</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>353</v>
+        <v>386</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25" s="3" customFormat="1" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -7225,383 +7425,383 @@
         <v>8</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="28" s="3" customFormat="1" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="29" s="3" customFormat="1" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="30" s="3" customFormat="1" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" s="3" customFormat="1" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="D31" s="11"/>
       <c r="E31" s="11" t="s">
-        <v>357</v>
+        <v>390</v>
       </c>
     </row>
     <row r="32" s="3" customFormat="1" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>347</v>
+        <v>380</v>
       </c>
       <c r="D32" s="11"/>
       <c r="E32" s="11"/>
     </row>
     <row r="33" s="3" customFormat="1" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="34" s="3" customFormat="1" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="35" s="3" customFormat="1" ht="115.2" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>358</v>
+        <v>391</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>360</v>
+        <v>393</v>
       </c>
     </row>
     <row r="36" s="3" customFormat="1" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="37" s="3" customFormat="1" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" s="3" customFormat="1" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="39" s="3" customFormat="1" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" s="3" customFormat="1" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="45" s="3" customFormat="1" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="46" s="3" customFormat="1" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
     </row>
     <row r="47" s="3" customFormat="1" ht="28.8" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:5">
       <c r="A49" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>359</v>
+        <v>392</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" s="3" customFormat="1" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="53" s="3" customFormat="1" ht="100.8" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>364</v>
+        <v>397</v>
       </c>
     </row>
     <row r="54" s="3" customFormat="1" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>349</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" s="3" customFormat="1" spans="1:5">
       <c r="A60" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" s="3" customFormat="1" spans="1:5">
       <c r="A61" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="62" s="3" customFormat="1" spans="1:5">
       <c r="A62" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="63" s="3" customFormat="1" spans="1:5">
       <c r="A63" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="64" s="3" customFormat="1" spans="1:5">
       <c r="A64" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -7626,19 +7826,19 @@
   <sheetData>
     <row r="1" ht="15.15" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" ht="15.15" hidden="1" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B2" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A9)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
         <v>postoji u Sheet1</v>
       </c>
       <c r="F2" t="s">
-        <v>366</v>
+        <v>399</v>
       </c>
       <c r="G2" t="str">
         <f>IF(ISNUMBER(MATCH(B2,Sheet3!$A:$A,0)),"on","off")</f>
@@ -7647,7 +7847,7 @@
     </row>
     <row r="3" ht="15.15" hidden="1" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B3" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A10)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7656,7 +7856,7 @@
     </row>
     <row r="4" ht="15.15" hidden="1" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B4" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A11)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7665,7 +7865,7 @@
     </row>
     <row r="5" ht="15.15" hidden="1" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B5" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A12)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7674,7 +7874,7 @@
     </row>
     <row r="6" ht="15.15" hidden="1" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B6" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A13)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7683,7 +7883,7 @@
     </row>
     <row r="7" ht="15.15" hidden="1" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B7" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A14)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7692,7 +7892,7 @@
     </row>
     <row r="8" ht="15.15" hidden="1" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B8" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A15)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7701,7 +7901,7 @@
     </row>
     <row r="9" ht="15.15" hidden="1" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A16)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7710,7 +7910,7 @@
     </row>
     <row r="10" ht="15.15" hidden="1" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B10" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A17)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7719,7 +7919,7 @@
     </row>
     <row r="11" ht="15.15" hidden="1" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B11" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A18)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7728,7 +7928,7 @@
     </row>
     <row r="12" ht="15.15" hidden="1" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B12" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A19)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7737,7 +7937,7 @@
     </row>
     <row r="13" ht="15.15" hidden="1" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B13" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A20)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7746,7 +7946,7 @@
     </row>
     <row r="14" ht="15.15" hidden="1" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B14" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A21)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7755,7 +7955,7 @@
     </row>
     <row r="15" ht="15.15" hidden="1" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B15" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A22)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7764,7 +7964,7 @@
     </row>
     <row r="16" ht="15.15" hidden="1" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A23)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7773,7 +7973,7 @@
     </row>
     <row r="17" ht="15.15" hidden="1" spans="1:2">
       <c r="A17" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B17" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A24)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7782,7 +7982,7 @@
     </row>
     <row r="18" ht="15.15" hidden="1" spans="1:2">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B18" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A25)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7791,7 +7991,7 @@
     </row>
     <row r="19" ht="15.15" hidden="1" spans="1:2">
       <c r="A19" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B19" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A26)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7800,7 +8000,7 @@
     </row>
     <row r="20" ht="15.15" hidden="1" spans="1:2">
       <c r="A20" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B20" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A27)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7809,7 +8009,7 @@
     </row>
     <row r="21" ht="15.15" hidden="1" spans="1:2">
       <c r="A21" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B21" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A28)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7818,7 +8018,7 @@
     </row>
     <row r="22" ht="15.15" hidden="1" spans="1:2">
       <c r="A22" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B22" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A29)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7827,7 +8027,7 @@
     </row>
     <row r="23" ht="15.15" hidden="1" spans="1:2">
       <c r="A23" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B23" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A30)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7836,7 +8036,7 @@
     </row>
     <row r="24" ht="15.15" hidden="1" spans="1:2">
       <c r="A24" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B24" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A31)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7845,7 +8045,7 @@
     </row>
     <row r="25" ht="15.15" hidden="1" spans="1:2">
       <c r="A25" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A32)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7854,7 +8054,7 @@
     </row>
     <row r="26" ht="15.15" hidden="1" spans="1:2">
       <c r="A26" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A33)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7863,7 +8063,7 @@
     </row>
     <row r="27" ht="15.15" hidden="1" spans="1:2">
       <c r="A27" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B27" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A34)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7872,7 +8072,7 @@
     </row>
     <row r="28" ht="15.15" hidden="1" spans="1:2">
       <c r="A28" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B28" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A35)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7881,7 +8081,7 @@
     </row>
     <row r="29" ht="15.15" hidden="1" spans="1:2">
       <c r="A29" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B29" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A36)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7890,7 +8090,7 @@
     </row>
     <row r="30" ht="15.15" hidden="1" spans="1:2">
       <c r="A30" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A37)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7899,7 +8099,7 @@
     </row>
     <row r="31" ht="15.15" hidden="1" spans="1:2">
       <c r="A31" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B31" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A38)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7908,7 +8108,7 @@
     </row>
     <row r="32" ht="15.15" hidden="1" spans="1:2">
       <c r="A32" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B32" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A39)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7917,7 +8117,7 @@
     </row>
     <row r="33" ht="15.15" hidden="1" spans="1:2">
       <c r="A33" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B33" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A40)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7926,7 +8126,7 @@
     </row>
     <row r="34" ht="15.15" hidden="1" spans="1:2">
       <c r="A34" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B34" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A41)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7935,7 +8135,7 @@
     </row>
     <row r="35" ht="15.15" hidden="1" spans="1:2">
       <c r="A35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B35" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A42)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7944,7 +8144,7 @@
     </row>
     <row r="36" ht="15.15" hidden="1" spans="1:2">
       <c r="A36" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B36" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A43)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7953,7 +8153,7 @@
     </row>
     <row r="37" ht="15.15" hidden="1" spans="1:2">
       <c r="A37" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B37" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A44)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7962,7 +8162,7 @@
     </row>
     <row r="38" ht="15.15" hidden="1" spans="1:2">
       <c r="A38" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B38" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A45)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7971,7 +8171,7 @@
     </row>
     <row r="39" ht="15.15" hidden="1" spans="1:2">
       <c r="A39" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B39" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A46)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7980,7 +8180,7 @@
     </row>
     <row r="40" ht="15.15" hidden="1" spans="1:2">
       <c r="A40" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B40" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A47)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7989,7 +8189,7 @@
     </row>
     <row r="41" ht="15.15" hidden="1" spans="1:2">
       <c r="A41" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B41" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A48)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -7998,7 +8198,7 @@
     </row>
     <row r="42" ht="15.15" hidden="1" spans="1:2">
       <c r="A42" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B42" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A49)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8007,7 +8207,7 @@
     </row>
     <row r="43" ht="15.15" hidden="1" spans="1:2">
       <c r="A43" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B43" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A50)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8016,7 +8216,7 @@
     </row>
     <row r="44" ht="15.15" hidden="1" spans="1:2">
       <c r="A44" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B44" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A51)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8034,7 +8234,7 @@
     </row>
     <row r="46" ht="15.15" hidden="1" spans="1:2">
       <c r="A46" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B46" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A53)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8043,7 +8243,7 @@
     </row>
     <row r="47" ht="15.15" hidden="1" spans="1:2">
       <c r="A47" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B47" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A54)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8052,7 +8252,7 @@
     </row>
     <row r="48" ht="15.15" hidden="1" spans="1:2">
       <c r="A48" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B48" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A55)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8061,7 +8261,7 @@
     </row>
     <row r="49" ht="15.15" hidden="1" spans="1:2">
       <c r="A49" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B49" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A56)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8070,7 +8270,7 @@
     </row>
     <row r="50" ht="15.15" hidden="1" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B50" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A57)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8079,7 +8279,7 @@
     </row>
     <row r="51" ht="15.15" spans="1:2">
       <c r="A51" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B51" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A58)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8088,7 +8288,7 @@
     </row>
     <row r="52" ht="15.15" spans="1:2">
       <c r="A52" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B52" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A59)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8097,7 +8297,7 @@
     </row>
     <row r="53" ht="15.15" spans="1:2">
       <c r="A53" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B53" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A60)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8106,7 +8306,7 @@
     </row>
     <row r="54" ht="15.15" spans="1:2">
       <c r="A54" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B54" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A61)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8115,7 +8315,7 @@
     </row>
     <row r="55" ht="15.15" spans="1:2">
       <c r="A55" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A62)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8124,7 +8324,7 @@
     </row>
     <row r="56" ht="15.15" spans="1:2">
       <c r="A56" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B56" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A63)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
@@ -8133,7 +8333,7 @@
     </row>
     <row r="57" ht="15.15" spans="1:2">
       <c r="A57" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B57" t="str">
         <f>IF(COUNTIF(Sheet1!$B:$AB,A64)&gt;0,"postoji u Sheet1","NE POSTOJI u Sheet1")</f>
